--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05019999999999999</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E2">
-        <v>0.021</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F2">
-        <v>0.155</v>
+        <v>0.105</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>9.062322325276496e-05</v>
+        <v>6.826793230486596e-05</v>
       </c>
       <c r="J2">
-        <v>8.962739681200752e-05</v>
+        <v>6.712691453290785e-05</v>
       </c>
       <c r="K2">
-        <v>8839.940000000001</v>
+        <v>13257.2</v>
       </c>
       <c r="L2">
-        <v>0.5043900490699532</v>
+        <v>0.5714556661925083</v>
       </c>
       <c r="M2">
-        <v>7375.5</v>
+        <v>4768.8</v>
       </c>
       <c r="N2">
-        <v>0.05548876456904517</v>
+        <v>0.03766348644721047</v>
       </c>
       <c r="O2">
-        <v>0.8343382421147655</v>
+        <v>0.3597139667501433</v>
       </c>
       <c r="P2">
-        <v>4786.6</v>
+        <v>4768.8</v>
       </c>
       <c r="Q2">
-        <v>0.0360114596279834</v>
+        <v>0.03766348644721047</v>
       </c>
       <c r="R2">
-        <v>0.5414742633999778</v>
+        <v>0.3597139667501433</v>
       </c>
       <c r="S2">
-        <v>2588.9</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.3510134906108061</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>88988.5</v>
+        <v>100956.8</v>
       </c>
       <c r="V2">
-        <v>0.6694952106097859</v>
+        <v>0.7973463069438302</v>
       </c>
       <c r="W2">
-        <v>0.07862094126231302</v>
+        <v>0.1297614148899824</v>
       </c>
       <c r="X2">
-        <v>0.05164074605353357</v>
+        <v>0.09626738513773715</v>
       </c>
       <c r="Y2">
-        <v>0.02698019520877944</v>
+        <v>0.03349402975224529</v>
       </c>
       <c r="Z2">
-        <v>0.1772312211380042</v>
+        <v>0.1834827102687285</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03496243229566363</v>
+        <v>0.07718827817184556</v>
       </c>
       <c r="AC2">
-        <v>-0.03496243229566363</v>
+        <v>-0.07718827817184556</v>
       </c>
       <c r="AD2">
-        <v>123792.57</v>
+        <v>135525.975</v>
       </c>
       <c r="AE2">
-        <v>2.358686946360207</v>
+        <v>1.831261192297072</v>
       </c>
       <c r="AF2">
-        <v>123794.9286869464</v>
+        <v>135527.8062611923</v>
       </c>
       <c r="AG2">
-        <v>34806.42868694637</v>
+        <v>34571.00626119231</v>
       </c>
       <c r="AH2">
-        <v>0.4822294830905209</v>
+        <v>0.5169979340505815</v>
       </c>
       <c r="AI2">
-        <v>0.5547883282248435</v>
+        <v>0.5606269243077237</v>
       </c>
       <c r="AJ2">
-        <v>0.2075205320000572</v>
+        <v>0.2144776248599865</v>
       </c>
       <c r="AK2">
-        <v>0.2594580060744348</v>
+        <v>0.2455562481041677</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>60093.48058252427</v>
+        <v>69500.5</v>
       </c>
       <c r="AP2">
-        <v>16896.32460531377</v>
+        <v>17728.7211595858</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank Of Sharjah P.J.S.C. (ADX:BOS)</t>
+          <t>Commercial Bank International P.S.C. (ADX:CBI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,7 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0268</v>
+        <v>-0.00659</v>
+      </c>
+      <c r="E3">
+        <v>0.177</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-567.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L3">
-        <v>-3.627237851662404</v>
+        <v>0.447035309793471</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,61 +758,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1445.9</v>
+        <v>284.4</v>
       </c>
       <c r="V3">
-        <v>3.893107162089392</v>
+        <v>0.7081673306772908</v>
       </c>
       <c r="W3">
-        <v>-0.641596923772902</v>
+        <v>0.1044032985840983</v>
       </c>
       <c r="X3">
-        <v>0.1057420124604905</v>
+        <v>0.06882493172180457</v>
       </c>
       <c r="Y3">
-        <v>-0.7473389362333925</v>
+        <v>0.03557836686229375</v>
       </c>
       <c r="Z3">
-        <v>0.1191165270373191</v>
+        <v>0.6572954983359607</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.02706378103360028</v>
+        <v>0.06881689524371808</v>
       </c>
       <c r="AC3">
-        <v>-0.02706378103360028</v>
+        <v>-0.06881689524371808</v>
       </c>
       <c r="AD3">
-        <v>1993.5</v>
+        <v>0.415</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1993.5</v>
+        <v>0.415</v>
       </c>
       <c r="AG3">
-        <v>547.5999999999999</v>
+        <v>-283.985</v>
       </c>
       <c r="AH3">
-        <v>0.8429531904097425</v>
+        <v>0.001032299789808838</v>
       </c>
       <c r="AI3">
-        <v>0.6602742448330684</v>
+        <v>0.0005857321298772785</v>
       </c>
       <c r="AJ3">
-        <v>0.5958650707290533</v>
+        <v>-2.414530459550225</v>
       </c>
       <c r="AK3">
-        <v>0.3480582215724909</v>
+        <v>-0.6695943317260646</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC (DFM:EMIRATESNBD)</t>
+          <t>National Bank of Umm Al-Qaiwain (PSC) (ADX:NBQ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,13 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0614</v>
+        <v>-0.0211</v>
       </c>
       <c r="E4">
-        <v>0.0273</v>
-      </c>
-      <c r="F4">
-        <v>0.14</v>
+        <v>-0.012</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2341.6</v>
+        <v>89.7</v>
       </c>
       <c r="L4">
-        <v>0.5077630323531962</v>
+        <v>0.6894696387394312</v>
       </c>
       <c r="M4">
-        <v>1947.4</v>
+        <v>40.2</v>
       </c>
       <c r="N4">
-        <v>0.08357114962900658</v>
+        <v>0.041243459526008</v>
       </c>
       <c r="O4">
-        <v>0.8316535702084046</v>
+        <v>0.4481605351170569</v>
       </c>
       <c r="P4">
-        <v>858.4</v>
+        <v>40.2</v>
       </c>
       <c r="Q4">
-        <v>0.03683756539054085</v>
+        <v>0.041243459526008</v>
       </c>
       <c r="R4">
-        <v>0.3665869490946361</v>
+        <v>0.4481605351170569</v>
       </c>
       <c r="S4">
-        <v>1089</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.5592071479921947</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>5930.1</v>
+        <v>646.4</v>
       </c>
       <c r="V4">
-        <v>0.2544856087167361</v>
+        <v>0.6631784138709346</v>
       </c>
       <c r="W4">
-        <v>0.1040013146732637</v>
+        <v>0.06714574444194925</v>
       </c>
       <c r="X4">
-        <v>0.0582655217249204</v>
+        <v>0.06883701846415498</v>
       </c>
       <c r="Y4">
-        <v>0.04573579294834332</v>
+        <v>-0.00169127402220573</v>
       </c>
       <c r="Z4">
-        <v>0.1094414489671932</v>
+        <v>0.7621558289396599</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03157646397843881</v>
+        <v>0.06883128549182614</v>
       </c>
       <c r="AC4">
-        <v>-0.03157646397843881</v>
+        <v>-0.06883128549182614</v>
       </c>
       <c r="AD4">
-        <v>32440.7</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>32440.7</v>
+        <v>1.4</v>
       </c>
       <c r="AG4">
-        <v>26510.6</v>
+        <v>-645</v>
       </c>
       <c r="AH4">
-        <v>0.581969036470947</v>
+        <v>0.001434279274664481</v>
       </c>
       <c r="AI4">
-        <v>0.5824737362801129</v>
+        <v>0.0009828009828009828</v>
       </c>
       <c r="AJ4">
-        <v>0.5322035055176471</v>
+        <v>-1.956323930846223</v>
       </c>
       <c r="AK4">
-        <v>0.5327200459764572</v>
+        <v>-0.82894229533479</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
+          <t>Ajman Bank PJSC (DFM:AJMANBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,13 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.05019999999999999</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E5">
-        <v>0.021</v>
-      </c>
-      <c r="F5">
-        <v>0.17</v>
+        <v>0.0222</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,85 +978,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1308.8</v>
+        <v>37.7</v>
       </c>
       <c r="L5">
-        <v>0.5265741299537317</v>
+        <v>0.306753458096013</v>
       </c>
       <c r="M5">
-        <v>558.7</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03459914044018381</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4268795843520783</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>558.7</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03459914044018381</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4268795843520783</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>639.2</v>
+        <v>394.4</v>
       </c>
       <c r="V5">
-        <v>0.03958433966236887</v>
+        <v>0.584556099006966</v>
       </c>
       <c r="W5">
-        <v>0.08737799260277997</v>
+        <v>0.05330128658277959</v>
       </c>
       <c r="X5">
-        <v>0.05986610483511221</v>
+        <v>0.06888106922246501</v>
       </c>
       <c r="Y5">
-        <v>0.02751188776766775</v>
+        <v>-0.01557978263968542</v>
       </c>
       <c r="Z5">
-        <v>0.07265292043986367</v>
+        <v>0.5548783240778368</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03204488546068467</v>
+        <v>0.06883605300236548</v>
       </c>
       <c r="AC5">
-        <v>-0.03204488546068467</v>
+        <v>-0.06883605300236548</v>
       </c>
       <c r="AD5">
-        <v>24644.6</v>
+        <v>1.96</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>24644.6</v>
+        <v>1.96</v>
       </c>
       <c r="AG5">
-        <v>24005.4</v>
+        <v>-392.44</v>
       </c>
       <c r="AH5">
-        <v>0.6041468508839882</v>
+        <v>0.002896580261874501</v>
       </c>
       <c r="AI5">
-        <v>0.6088092885375493</v>
+        <v>0.002863571282470853</v>
       </c>
       <c r="AJ5">
-        <v>0.5978452526822271</v>
+        <v>-1.390349323318925</v>
       </c>
       <c r="AK5">
-        <v>0.6025330816650268</v>
+        <v>-1.352961456250431</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
+          <t>Abu Dhabi Islamic Bank PJSC (ADX:ADIB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.136</v>
+        <v>0.0302</v>
       </c>
       <c r="E6">
-        <v>0.0268</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1097,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>139</v>
+        <v>865.2</v>
       </c>
       <c r="L6">
-        <v>0.4596560846560847</v>
+        <v>0.5855837563451777</v>
       </c>
       <c r="M6">
-        <v>92.09999999999999</v>
+        <v>376.8</v>
       </c>
       <c r="N6">
-        <v>0.05629584352078239</v>
+        <v>0.04182809187083024</v>
       </c>
       <c r="O6">
-        <v>0.6625899280575539</v>
+        <v>0.435506241331484</v>
       </c>
       <c r="P6">
-        <v>92.09999999999999</v>
+        <v>376.8</v>
       </c>
       <c r="Q6">
-        <v>0.05629584352078239</v>
+        <v>0.04182809187083024</v>
       </c>
       <c r="R6">
-        <v>0.6625899280575539</v>
+        <v>0.435506241331484</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1127,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2404.7</v>
+        <v>881.7</v>
       </c>
       <c r="V6">
-        <v>1.469865525672372</v>
+        <v>0.09787640287290611</v>
       </c>
       <c r="W6">
-        <v>0.0667948101874099</v>
+        <v>0.1595632849528798</v>
       </c>
       <c r="X6">
-        <v>0.05918249743534421</v>
+        <v>0.06897739734746043</v>
       </c>
       <c r="Y6">
-        <v>0.007612312752065691</v>
+        <v>0.09058588760541934</v>
       </c>
       <c r="Z6">
-        <v>0.09042791782542388</v>
+        <v>0.4356350984785942</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03258803445535699</v>
+        <v>0.06888233085487587</v>
       </c>
       <c r="AC6">
-        <v>-0.03258803445535699</v>
+        <v>-0.06888233085487587</v>
       </c>
       <c r="AD6">
-        <v>2403.2</v>
+        <v>55.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2403.2</v>
+        <v>55.1</v>
       </c>
       <c r="AG6">
-        <v>-1.5</v>
+        <v>-826.6</v>
       </c>
       <c r="AH6">
-        <v>0.5949693008516538</v>
+        <v>0.006079396253061765</v>
       </c>
       <c r="AI6">
-        <v>0.5338427705089188</v>
+        <v>0.009468818202127477</v>
       </c>
       <c r="AJ6">
-        <v>-0.0009177118384827164</v>
+        <v>-0.1010303482161409</v>
       </c>
       <c r="AK6">
-        <v>-0.000715307582260372</v>
+        <v>-0.1674160489326366</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al-Khaimah (P.S.C.) (ADX:RAKBANK)</t>
+          <t>Dubai Islamic Bank P.J.S.C. (DFM:DIB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,10 +1201,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0212</v>
+        <v>0.0414</v>
       </c>
       <c r="E7">
-        <v>-0.0707</v>
+        <v>0.0563</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,28 +1219,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>163.4</v>
+        <v>1464</v>
       </c>
       <c r="L7">
-        <v>0.3016429758168728</v>
+        <v>0.6588065880658807</v>
       </c>
       <c r="M7">
-        <v>68.5</v>
+        <v>601.8</v>
       </c>
       <c r="N7">
-        <v>0.03335443346155719</v>
+        <v>0.05365788417814631</v>
       </c>
       <c r="O7">
-        <v>0.4192166462668299</v>
+        <v>0.4110655737704918</v>
       </c>
       <c r="P7">
-        <v>68.5</v>
+        <v>601.8</v>
       </c>
       <c r="Q7">
-        <v>0.03335443346155719</v>
+        <v>0.05365788417814631</v>
       </c>
       <c r="R7">
-        <v>0.4192166462668299</v>
+        <v>0.4110655737704918</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1249,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>624.9</v>
+        <v>1914</v>
       </c>
       <c r="V7">
-        <v>0.3042800798558699</v>
+        <v>0.1706566804868263</v>
       </c>
       <c r="W7">
-        <v>0.07830170596128043</v>
+        <v>0.1412186863961261</v>
       </c>
       <c r="X7">
-        <v>0.05386751712652048</v>
+        <v>0.08431413795709661</v>
       </c>
       <c r="Y7">
-        <v>0.02443418883475995</v>
+        <v>0.05690454843902953</v>
       </c>
       <c r="Z7">
-        <v>0.160827741820557</v>
+        <v>0.2246053083749419</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03289166455523265</v>
+        <v>0.07375200734687898</v>
       </c>
       <c r="AC7">
-        <v>-0.03289166455523265</v>
+        <v>-0.07375200734687898</v>
       </c>
       <c r="AD7">
-        <v>2102.8</v>
+        <v>5803.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2102.8</v>
+        <v>5803.4</v>
       </c>
       <c r="AG7">
-        <v>1477.9</v>
+        <v>3889.4</v>
       </c>
       <c r="AH7">
-        <v>0.5059064116444124</v>
+        <v>0.3409973617566352</v>
       </c>
       <c r="AI7">
-        <v>0.4866128248443756</v>
+        <v>0.3306931370090945</v>
       </c>
       <c r="AJ7">
-        <v>0.4184788764299468</v>
+        <v>0.2574926017385087</v>
       </c>
       <c r="AK7">
-        <v>0.3998214478952494</v>
+        <v>0.24875920998772</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,7 +1314,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
+          <t>United Arab Bank P.J.S.C. (ADX:UAB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,15 +1322,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.197</v>
-      </c>
-      <c r="E8">
-        <v>0.149</v>
-      </c>
-      <c r="F8">
-        <v>0.118</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1350,85 +1335,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3386</v>
+        <v>39.3</v>
       </c>
       <c r="L8">
-        <v>0.6587164173297279</v>
+        <v>0.3697083725305738</v>
       </c>
       <c r="M8">
-        <v>2209.8</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.03947840907263792</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.6526284701712937</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>2209.8</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.03947840907263792</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.6526284701712937</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>63756</v>
+        <v>358.1</v>
       </c>
       <c r="V8">
-        <v>1.139010520786996</v>
+        <v>0.7502618897967736</v>
       </c>
       <c r="W8">
-        <v>0.1230234856412045</v>
+        <v>0.09629992648860572</v>
       </c>
       <c r="X8">
-        <v>0.05233224669768348</v>
+        <v>0.08045719847349594</v>
       </c>
       <c r="Y8">
-        <v>0.07069123894352103</v>
+        <v>0.01584272801510977</v>
       </c>
       <c r="Z8">
-        <v>-1.311568687487241</v>
+        <v>0.4650043744531934</v>
       </c>
       <c r="AA8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03363138231718132</v>
+        <v>0.07608463992137077</v>
       </c>
       <c r="AC8">
-        <v>-0.03363138231718132</v>
+        <v>-0.07608463992137077</v>
       </c>
       <c r="AD8">
-        <v>50117.4</v>
+        <v>185.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>50117.4</v>
+        <v>185.6</v>
       </c>
       <c r="AG8">
-        <v>-13638.6</v>
+        <v>-172.5</v>
       </c>
       <c r="AH8">
-        <v>0.4723943207942518</v>
+        <v>0.2799818977221301</v>
       </c>
       <c r="AI8">
-        <v>0.6275547385845979</v>
+        <v>0.3301903575876178</v>
       </c>
       <c r="AJ8">
-        <v>-0.322149077741796</v>
+        <v>-0.565944881889764</v>
       </c>
       <c r="AK8">
-        <v>-0.8468339811491796</v>
+        <v>-0.8455882352941179</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1445,7 +1427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dubai Islamic Bank P.J.S.C. (DFM:DIB)</t>
+          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,13 +1436,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.00281</v>
+        <v>0.131</v>
       </c>
       <c r="E9">
-        <v>-0.0186</v>
-      </c>
-      <c r="F9">
-        <v>0.188</v>
+        <v>0.127</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,85 +1454,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>878.6</v>
+        <v>3885.3</v>
       </c>
       <c r="L9">
-        <v>0.513260894964365</v>
+        <v>0.6481657574695961</v>
       </c>
       <c r="M9">
-        <v>2028.4</v>
+        <v>1509.8</v>
       </c>
       <c r="N9">
-        <v>0.1916133725049358</v>
+        <v>0.02937188368749623</v>
       </c>
       <c r="O9">
-        <v>2.308672888686547</v>
+        <v>0.3885929014490515</v>
       </c>
       <c r="P9">
-        <v>528.5</v>
+        <v>1509.8</v>
       </c>
       <c r="Q9">
-        <v>0.04992490010296716</v>
+        <v>0.02937188368749623</v>
       </c>
       <c r="R9">
-        <v>0.6015251536535398</v>
+        <v>0.3885929014490515</v>
       </c>
       <c r="S9">
-        <v>1499.9</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.7394498126602248</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>7132.2</v>
+        <v>66746.10000000001</v>
       </c>
       <c r="V9">
-        <v>0.6737452649278758</v>
+        <v>1.298488995757049</v>
       </c>
       <c r="W9">
-        <v>0.08650447487865152</v>
+        <v>0.1306444291262462</v>
       </c>
       <c r="X9">
-        <v>0.04915189559665101</v>
+        <v>0.09809519316842834</v>
       </c>
       <c r="Y9">
-        <v>0.03735257928200052</v>
+        <v>0.0325492359578179</v>
       </c>
       <c r="Z9">
-        <v>0.2006423179708378</v>
+        <v>0.5314661134163212</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.03496243229566363</v>
+        <v>0.07691786639627625</v>
       </c>
       <c r="AC9">
-        <v>-0.03496243229566363</v>
+        <v>-0.07691786639627625</v>
       </c>
       <c r="AD9">
-        <v>6659.1</v>
+        <v>50215.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>6659.1</v>
+        <v>50215.8</v>
       </c>
       <c r="AG9">
-        <v>-473.0999999999995</v>
+        <v>-16530.3</v>
       </c>
       <c r="AH9">
-        <v>0.3861467091910699</v>
+        <v>0.4941590474981475</v>
       </c>
       <c r="AI9">
-        <v>0.3755265695579353</v>
+        <v>0.6212005190711644</v>
       </c>
       <c r="AJ9">
-        <v>-0.04678229570445371</v>
+        <v>-0.4740197174859346</v>
       </c>
       <c r="AK9">
-        <v>-0.04462997028442049</v>
+        <v>-1.173143797992989</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1549,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Commercial Bank of Dubai PSC (DFM:CBD)</t>
+          <t>Emirates NBD Bank PJSC (DFM:EMIRATESNBD)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,10 +1558,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.052</v>
+        <v>0.132</v>
       </c>
       <c r="E10">
-        <v>0.09720000000000001</v>
+        <v>0.0667</v>
+      </c>
+      <c r="F10">
+        <v>0.11</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1591,34 +1573,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.002623926335251873</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.002623926335251873</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>369</v>
+        <v>3017.8</v>
       </c>
       <c r="L10">
-        <v>0.6096150669089708</v>
+        <v>0.4662207047845634</v>
       </c>
       <c r="M10">
-        <v>152.6</v>
+        <v>998</v>
       </c>
       <c r="N10">
-        <v>0.04597354863977344</v>
+        <v>0.04464046089710329</v>
       </c>
       <c r="O10">
-        <v>0.413550135501355</v>
+        <v>0.3307044867121744</v>
       </c>
       <c r="P10">
-        <v>152.6</v>
+        <v>998</v>
       </c>
       <c r="Q10">
-        <v>0.04597354863977344</v>
+        <v>0.04464046089710329</v>
       </c>
       <c r="R10">
-        <v>0.413550135501355</v>
+        <v>0.3307044867121744</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1627,67 +1609,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1987.1</v>
+        <v>11661.9</v>
       </c>
       <c r="V10">
-        <v>0.5986503178380983</v>
+        <v>0.5216358626612513</v>
       </c>
       <c r="W10">
-        <v>0.1287643507694455</v>
+        <v>0.1298604058729367</v>
       </c>
       <c r="X10">
-        <v>0.05164074605353357</v>
+        <v>0.1130293726382527</v>
       </c>
       <c r="Y10">
-        <v>0.07712360471591193</v>
+        <v>0.01683103323468392</v>
       </c>
       <c r="Z10">
-        <v>0.1173298792897066</v>
+        <v>0.1496361333037431</v>
       </c>
       <c r="AA10">
-        <v>0.0003078649601801846</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.03533056690040492</v>
+        <v>0.07745868994741489</v>
       </c>
       <c r="AC10">
-        <v>-0.03502270194022473</v>
+        <v>-0.07745868994741489</v>
       </c>
       <c r="AD10">
-        <v>2777.4</v>
+        <v>32971.5</v>
       </c>
       <c r="AE10">
-        <v>2.358686946360207</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2779.75868694636</v>
+        <v>32971.5</v>
       </c>
       <c r="AG10">
-        <v>792.6586869463604</v>
+        <v>21309.6</v>
       </c>
       <c r="AH10">
-        <v>0.4557684766824424</v>
+        <v>0.595928997847379</v>
       </c>
       <c r="AI10">
-        <v>0.4347612762773762</v>
+        <v>0.5773220967552718</v>
       </c>
       <c r="AJ10">
-        <v>0.1927691271468021</v>
+        <v>0.4880135574588925</v>
       </c>
       <c r="AK10">
-        <v>0.1798774861539461</v>
+        <v>0.4688663386814289</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>1348.252427184466</v>
-      </c>
-      <c r="AP10">
-        <v>384.7857703623109</v>
       </c>
     </row>
     <row r="11">
@@ -1698,7 +1674,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank PJSC (DFM:EIB)</t>
+          <t>Commercial Bank of Dubai PSC (DFM:CBD)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1707,10 +1683,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0591</v>
+        <v>0.0759</v>
       </c>
       <c r="E11">
-        <v>0.243</v>
+        <v>0.122</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,94 +1695,103 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.002124695145613879</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.002124695145613879</v>
       </c>
       <c r="K11">
-        <v>172.4</v>
+        <v>468.6</v>
       </c>
       <c r="L11">
-        <v>0.361501362969176</v>
+        <v>0.6286557552991683</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>233.5</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.06334780249593054</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.4982927870251814</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>233.5</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.06334780249593054</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.4982927870251814</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>944.4</v>
+        <v>1272</v>
       </c>
       <c r="V11">
-        <v>0.08551094692236648</v>
+        <v>0.3450895279435703</v>
       </c>
       <c r="W11">
-        <v>0.07862094126231302</v>
+        <v>0.1296624239070282</v>
       </c>
       <c r="X11">
-        <v>0.04222236975597948</v>
+        <v>0.09443957710704597</v>
       </c>
       <c r="Y11">
-        <v>0.03639857150633354</v>
+        <v>0.03522284679998226</v>
       </c>
       <c r="Z11">
-        <v>0.3901341623036649</v>
+        <v>0.1691733531783833</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.0003594418022653334</v>
       </c>
       <c r="AB11">
-        <v>0.04083441757454617</v>
+        <v>0.0807963667457938</v>
       </c>
       <c r="AC11">
-        <v>-0.04083441757454617</v>
+        <v>-0.08043692494352846</v>
       </c>
       <c r="AD11">
-        <v>539.2</v>
+        <v>3149.8</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.831261192297072</v>
       </c>
       <c r="AF11">
-        <v>539.2</v>
+        <v>3151.631261192297</v>
       </c>
       <c r="AG11">
-        <v>-405.1999999999999</v>
+        <v>1879.631261192297</v>
       </c>
       <c r="AH11">
-        <v>0.04654937237771293</v>
+        <v>0.4609244255506604</v>
       </c>
       <c r="AI11">
-        <v>0.1868653612892047</v>
+        <v>0.4637594931454136</v>
       </c>
       <c r="AJ11">
-        <v>-0.03808628630510386</v>
+        <v>0.3377211268555426</v>
       </c>
       <c r="AK11">
-        <v>-0.2087476173303796</v>
+        <v>0.3402767340844851</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>1615.282051282051</v>
+      </c>
+      <c r="AP11">
+        <v>963.9134672781012</v>
       </c>
     </row>
     <row r="12">
@@ -1817,7 +1802,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>National Bank of Umm Al-Qaiwain (PSC) (ADX:NBQ)</t>
+          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1826,10 +1811,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0489</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="E12">
-        <v>-0.0604</v>
+        <v>0.0767</v>
+      </c>
+      <c r="F12">
+        <v>0.1</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1844,28 +1832,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>62.7</v>
+        <v>1658.6</v>
       </c>
       <c r="L12">
-        <v>0.6135029354207436</v>
+        <v>0.5642840132004218</v>
       </c>
       <c r="M12">
-        <v>40.2</v>
+        <v>750.4</v>
       </c>
       <c r="N12">
-        <v>0.0431886549204985</v>
+        <v>0.04407713498622589</v>
       </c>
       <c r="O12">
-        <v>0.6411483253588517</v>
+        <v>0.4524297600385868</v>
       </c>
       <c r="P12">
-        <v>40.2</v>
+        <v>750.4</v>
       </c>
       <c r="Q12">
-        <v>0.0431886549204985</v>
+        <v>0.04407713498622589</v>
       </c>
       <c r="R12">
-        <v>0.6411483253588517</v>
+        <v>0.4524297600385868</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1874,55 +1862,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1203.3</v>
+        <v>6067.1</v>
       </c>
       <c r="V12">
-        <v>1.292758917060593</v>
+        <v>0.3563704499932451</v>
       </c>
       <c r="W12">
-        <v>0.05023233456176895</v>
+        <v>0.104749273714791</v>
       </c>
       <c r="X12">
-        <v>0.04212814822805542</v>
+        <v>0.1134093170547064</v>
       </c>
       <c r="Y12">
-        <v>0.008104186333713528</v>
+        <v>-0.008660043339915463</v>
       </c>
       <c r="Z12">
-        <v>0.2723154809485744</v>
+        <v>0.07827175287930231</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04095936991995415</v>
+        <v>0.08089713314649558</v>
       </c>
       <c r="AC12">
-        <v>-0.04095936991995415</v>
+        <v>-0.08089713314649558</v>
       </c>
       <c r="AD12">
-        <v>38.1</v>
+        <v>25323.9</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>38.1</v>
+        <v>25323.9</v>
       </c>
       <c r="AG12">
-        <v>-1165.2</v>
+        <v>19256.8</v>
       </c>
       <c r="AH12">
-        <v>0.03932294354422541</v>
+        <v>0.5979867103044728</v>
       </c>
       <c r="AI12">
-        <v>0.0277292576419214</v>
+        <v>0.6124339775959138</v>
       </c>
       <c r="AJ12">
-        <v>4.970989761092149</v>
+        <v>0.5307608560836791</v>
       </c>
       <c r="AK12">
-        <v>-6.826010544815464</v>
+        <v>0.545788988875505</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1939,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Commercial Bank International P.S.C. (ADX:CBI)</t>
+          <t>Bank Of Sharjah P.J.S.C. (ADX:BOS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1948,7 +1936,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.274</v>
+        <v>-0.212</v>
+      </c>
+      <c r="E13">
+        <v>0.222</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1963,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-5.36</v>
+        <v>289.2</v>
       </c>
       <c r="L13">
-        <v>-0.066916354556804</v>
+        <v>5.047120418848167</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1975,7 +1966,7 @@
         <v>-0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -1984,61 +1975,61 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="U13">
-        <v>363.4</v>
+        <v>722.7</v>
       </c>
       <c r="V13">
-        <v>1.261367580701145</v>
+        <v>2.513739130434783</v>
       </c>
       <c r="W13">
-        <v>-0.008132301623425884</v>
+        <v>0.2825598436736688</v>
       </c>
       <c r="X13">
-        <v>0.04188304905182554</v>
+        <v>0.2359358029161075</v>
       </c>
       <c r="Y13">
-        <v>-0.05001535067525142</v>
+        <v>0.04662404075756127</v>
       </c>
       <c r="Z13">
-        <v>0.1739036039947894</v>
+        <v>0.03647126217299981</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04129345984969819</v>
+        <v>0.08112161852070784</v>
       </c>
       <c r="AC13">
-        <v>-0.04129345984969819</v>
+        <v>-0.08112161852070784</v>
       </c>
       <c r="AD13">
-        <v>5.88</v>
+        <v>1602.1</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>5.88</v>
+        <v>1602.1</v>
       </c>
       <c r="AG13">
-        <v>-357.52</v>
+        <v>879.3999999999999</v>
       </c>
       <c r="AH13">
-        <v>0.02000136063677801</v>
+        <v>0.8478513971210838</v>
       </c>
       <c r="AI13">
-        <v>0.008755472170106316</v>
+        <v>0.8056016493186504</v>
       </c>
       <c r="AJ13">
-        <v>5.150100835494096</v>
+        <v>0.7536207044305424</v>
       </c>
       <c r="AK13">
-        <v>-1.160101239535336</v>
+        <v>0.6946287519747234</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2055,7 +2046,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abu Dhabi Islamic Bank PJSC (ADX:ADIB)</t>
+          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2064,10 +2055,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.00033</v>
+        <v>0.0659</v>
       </c>
       <c r="E14">
-        <v>0.0108</v>
+        <v>0.051</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2082,28 +2073,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>567.2</v>
+        <v>170</v>
       </c>
       <c r="L14">
-        <v>0.4693421597021101</v>
+        <v>0.4773939904521202</v>
       </c>
       <c r="M14">
-        <v>277.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N14">
-        <v>0.04089323303843493</v>
+        <v>0.05629584352078239</v>
       </c>
       <c r="O14">
-        <v>0.4897743300423131</v>
+        <v>0.5417647058823529</v>
       </c>
       <c r="P14">
-        <v>277.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q14">
-        <v>0.04089323303843493</v>
+        <v>0.05629584352078239</v>
       </c>
       <c r="R14">
-        <v>0.4897743300423131</v>
+        <v>0.5417647058823529</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2112,55 +2103,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2069.7</v>
+        <v>1812.4</v>
       </c>
       <c r="V14">
-        <v>0.3046678344839768</v>
+        <v>1.107823960880196</v>
       </c>
       <c r="W14">
-        <v>0.1098884066955983</v>
+        <v>0.08101024541339051</v>
       </c>
       <c r="X14">
-        <v>0.04176043069417044</v>
+        <v>0.1173562476891574</v>
       </c>
       <c r="Y14">
-        <v>0.06812797600142784</v>
+        <v>-0.03634600227576691</v>
       </c>
       <c r="Z14">
-        <v>0.5339076651203888</v>
+        <v>0.1698140200286123</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.04146569311379522</v>
+        <v>0.08254231941054127</v>
       </c>
       <c r="AC14">
-        <v>-0.04146569311379522</v>
+        <v>-0.08254231941054127</v>
       </c>
       <c r="AD14">
-        <v>68.90000000000001</v>
+        <v>2648.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>68.90000000000001</v>
+        <v>2648.8</v>
       </c>
       <c r="AG14">
-        <v>-2000.8</v>
+        <v>836.4000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.01004051178922212</v>
+        <v>0.6181852128454071</v>
       </c>
       <c r="AI14">
-        <v>0.01254072550554231</v>
+        <v>0.5600236796481881</v>
       </c>
       <c r="AJ14">
-        <v>-0.4174856546687532</v>
+        <v>0.3382947743083644</v>
       </c>
       <c r="AK14">
-        <v>-0.5842775376708328</v>
+        <v>0.286693631315555</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2177,7 +2168,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ajman Bank PJSC (DFM:AJMANBANK)</t>
+          <t>Mashreqbank PSC (DFM:MASQ)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2186,10 +2177,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.00292</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="E15">
-        <v>-0.0786</v>
+        <v>0.0953</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2204,87 +2195,212 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>23.9</v>
+        <v>903.1</v>
       </c>
       <c r="L15">
-        <v>0.2313649564375605</v>
+        <v>0.5249055507120023</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>63.5</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.01192376302694583</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.07031336507584984</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>63.5</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.01192376302694583</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.07031336507584984</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>487.6</v>
+        <v>6810.8</v>
       </c>
       <c r="V15">
-        <v>1.035024410953089</v>
+        <v>1.278903389353112</v>
       </c>
       <c r="W15">
-        <v>0.034905798159778</v>
+        <v>0.1710935131858139</v>
       </c>
       <c r="X15">
-        <v>0.04168468147806625</v>
+        <v>0.1259325136821891</v>
       </c>
       <c r="Y15">
-        <v>-0.006778883318288256</v>
+        <v>0.04516099950362476</v>
       </c>
       <c r="Z15">
-        <v>0.2453040773194652</v>
+        <v>0.2024355806565478</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.04157385323903051</v>
+        <v>0.08337812204254386</v>
       </c>
       <c r="AC15">
-        <v>-0.04157385323903051</v>
+        <v>-0.08337812204254386</v>
       </c>
       <c r="AD15">
-        <v>1.79</v>
+        <v>10145.1</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.79</v>
+        <v>10145.1</v>
       </c>
       <c r="AG15">
-        <v>-485.81</v>
+        <v>3334.3</v>
       </c>
       <c r="AH15">
-        <v>0.003785235467021929</v>
+        <v>0.655766421470402</v>
       </c>
       <c r="AI15">
-        <v>0.002524362210720783</v>
+        <v>0.618607430533113</v>
       </c>
       <c r="AJ15">
-        <v>33.02583276682533</v>
+        <v>0.3850319868819142</v>
       </c>
       <c r="AK15">
-        <v>-2.19337216127139</v>
+        <v>0.34771772116257</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The National Bank of Ras Al-Khaimah (P.S.C.) (ADX:RAKBANK)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="E16">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>301.6</v>
+      </c>
+      <c r="L16">
+        <v>0.4283482459877859</v>
+      </c>
+      <c r="M16">
+        <v>102.7</v>
+      </c>
+      <c r="N16">
+        <v>0.04788102009417688</v>
+      </c>
+      <c r="O16">
+        <v>0.3405172413793103</v>
+      </c>
+      <c r="P16">
+        <v>102.7</v>
+      </c>
+      <c r="Q16">
+        <v>0.04788102009417688</v>
+      </c>
+      <c r="R16">
+        <v>0.3405172413793103</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>1384.8</v>
+      </c>
+      <c r="V16">
+        <v>0.6456245046389109</v>
+      </c>
+      <c r="W16">
+        <v>0.136612764415455</v>
+      </c>
+      <c r="X16">
+        <v>0.1166340497423925</v>
+      </c>
+      <c r="Y16">
+        <v>0.01997871467306249</v>
+      </c>
+      <c r="Z16">
+        <v>0.1934181248798176</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.0847991705767288</v>
+      </c>
+      <c r="AC16">
+        <v>-0.0847991705767288</v>
+      </c>
+      <c r="AD16">
+        <v>3421.1</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>3421.1</v>
+      </c>
+      <c r="AG16">
+        <v>2036.3</v>
+      </c>
+      <c r="AH16">
+        <v>0.6146424721523536</v>
+      </c>
+      <c r="AI16">
+        <v>0.5914969397282064</v>
+      </c>
+      <c r="AJ16">
+        <v>0.4870132976179087</v>
+      </c>
+      <c r="AK16">
+        <v>0.4629006592407365</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04480000000000001</v>
+        <v>0.06705</v>
       </c>
       <c r="E2">
-        <v>0.08160000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="F2">
-        <v>0.105</v>
+        <v>0.0308</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6.826793230486596e-05</v>
+        <v>2.552415948670868e-05</v>
       </c>
       <c r="J2">
-        <v>6.712691453290785e-05</v>
+        <v>2.48435899546132e-05</v>
       </c>
       <c r="K2">
-        <v>13257.2</v>
+        <v>18774.48</v>
       </c>
       <c r="L2">
-        <v>0.5714556661925083</v>
+        <v>0.5869794809425697</v>
       </c>
       <c r="M2">
-        <v>4768.8</v>
+        <v>6472.679</v>
       </c>
       <c r="N2">
-        <v>0.03766348644721047</v>
+        <v>0.04566476463807134</v>
       </c>
       <c r="O2">
-        <v>0.3597139667501433</v>
+        <v>0.3447594287564822</v>
       </c>
       <c r="P2">
-        <v>4768.8</v>
+        <v>5722.24</v>
       </c>
       <c r="Q2">
-        <v>0.03766348644721047</v>
+        <v>0.04037041583594016</v>
       </c>
       <c r="R2">
-        <v>0.3597139667501433</v>
+        <v>0.3047882018569888</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>750.4389999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1159394742115282</v>
       </c>
       <c r="U2">
-        <v>100956.8</v>
+        <v>99508</v>
       </c>
       <c r="V2">
-        <v>0.7973463069438302</v>
+        <v>0.702029159735127</v>
       </c>
       <c r="W2">
-        <v>0.1297614148899824</v>
+        <v>0.1640794021201019</v>
       </c>
       <c r="X2">
-        <v>0.09626738513773715</v>
+        <v>0.07523405381321557</v>
       </c>
       <c r="Y2">
-        <v>0.03349402975224529</v>
+        <v>0.08884534830688634</v>
       </c>
       <c r="Z2">
-        <v>0.1834827102687285</v>
+        <v>0.2379852276921246</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07718827817184556</v>
+        <v>0.05843554037618376</v>
       </c>
       <c r="AC2">
-        <v>-0.07718827817184556</v>
+        <v>-0.05843554037618376</v>
       </c>
       <c r="AD2">
-        <v>135525.975</v>
+        <v>139170.072</v>
       </c>
       <c r="AE2">
-        <v>1.831261192297072</v>
+        <v>1.918061556167858</v>
       </c>
       <c r="AF2">
-        <v>135527.8062611923</v>
+        <v>139171.9900615562</v>
       </c>
       <c r="AG2">
-        <v>34571.00626119231</v>
+        <v>39663.99006155616</v>
       </c>
       <c r="AH2">
-        <v>0.5169979340505815</v>
+        <v>0.4954231593757104</v>
       </c>
       <c r="AI2">
-        <v>0.5606269243077237</v>
+        <v>0.533223175664823</v>
       </c>
       <c r="AJ2">
-        <v>0.2144776248599865</v>
+        <v>0.218645944071502</v>
       </c>
       <c r="AK2">
-        <v>0.2455562481041677</v>
+        <v>0.2456075140068427</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>69500.5</v>
+        <v>115975.06</v>
       </c>
       <c r="AP2">
-        <v>17728.7211595858</v>
+        <v>33053.32505129681</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commercial Bank International P.S.C. (ADX:CBI)</t>
+          <t>Emirates NBD Bank PJSC (DFM:EMIRATESNBD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00659</v>
+        <v>0.206</v>
       </c>
       <c r="E3">
-        <v>0.177</v>
+        <v>0.168</v>
+      </c>
+      <c r="F3">
+        <v>0.113</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,82 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>67.09999999999999</v>
+        <v>5822.3</v>
       </c>
       <c r="L3">
-        <v>0.447035309793471</v>
+        <v>0.5469310688184569</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1169.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03931717580471147</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2009171633203373</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1169.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03931717580471147</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2009171633203373</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>284.4</v>
+        <v>14184.7</v>
       </c>
       <c r="V3">
-        <v>0.7081673306772908</v>
+        <v>0.4767501655300828</v>
       </c>
       <c r="W3">
-        <v>0.1044032985840983</v>
+        <v>0.2415230683713174</v>
       </c>
       <c r="X3">
-        <v>0.06882493172180457</v>
+        <v>0.07778118259248543</v>
       </c>
       <c r="Y3">
-        <v>0.03557836686229375</v>
+        <v>0.163741885778832</v>
       </c>
       <c r="Z3">
-        <v>0.6572954983359607</v>
+        <v>0.242455023948509</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06881689524371808</v>
+        <v>0.05642453088609365</v>
       </c>
       <c r="AC3">
-        <v>-0.06881689524371808</v>
+        <v>-0.05642453088609365</v>
       </c>
       <c r="AD3">
-        <v>0.415</v>
+        <v>34146.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.415</v>
+        <v>34146.2</v>
       </c>
       <c r="AG3">
-        <v>-283.985</v>
+        <v>19961.5</v>
       </c>
       <c r="AH3">
-        <v>0.001032299789808838</v>
+        <v>0.5343768535081088</v>
       </c>
       <c r="AI3">
-        <v>0.0005857321298772785</v>
+        <v>0.5436072474173792</v>
       </c>
       <c r="AJ3">
-        <v>-2.414530459550225</v>
+        <v>0.4015235022448224</v>
       </c>
       <c r="AK3">
-        <v>-0.6695943317260646</v>
+        <v>0.4104821363208265</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Bank of Umm Al-Qaiwain (PSC) (ADX:NBQ)</t>
+          <t>Commercial Bank of Dubai PSC (DFM:CBD)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0211</v>
+        <v>0.116</v>
       </c>
       <c r="E4">
-        <v>-0.012</v>
+        <v>0.156</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.000823469526696014</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.000823469526696014</v>
       </c>
       <c r="K4">
-        <v>89.7</v>
+        <v>663.9</v>
       </c>
       <c r="L4">
-        <v>0.6894696387394312</v>
+        <v>0.6696590679846681</v>
       </c>
       <c r="M4">
-        <v>40.2</v>
+        <v>234.8</v>
       </c>
       <c r="N4">
-        <v>0.041243459526008</v>
+        <v>0.05653335901572244</v>
       </c>
       <c r="O4">
-        <v>0.4481605351170569</v>
+        <v>0.3536677210423257</v>
       </c>
       <c r="P4">
-        <v>40.2</v>
+        <v>234.8</v>
       </c>
       <c r="Q4">
-        <v>0.041243459526008</v>
+        <v>0.05653335901572244</v>
       </c>
       <c r="R4">
-        <v>0.4481605351170569</v>
+        <v>0.3536677210423257</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,61 +892,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>646.4</v>
+        <v>528.5</v>
       </c>
       <c r="V4">
-        <v>0.6631784138709346</v>
+        <v>0.127248212264946</v>
       </c>
       <c r="W4">
-        <v>0.06714574444194925</v>
+        <v>0.1821799023105208</v>
       </c>
       <c r="X4">
-        <v>0.06883701846415498</v>
+        <v>0.07456958176556423</v>
       </c>
       <c r="Y4">
-        <v>-0.00169127402220573</v>
+        <v>0.1076103205449566</v>
       </c>
       <c r="Z4">
-        <v>0.7621558289396599</v>
+        <v>0.1794740597076685</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.0001477914190016859</v>
       </c>
       <c r="AB4">
-        <v>0.06883128549182614</v>
+        <v>0.05672925212760981</v>
       </c>
       <c r="AC4">
-        <v>-0.06883128549182614</v>
+        <v>-0.05658146070860812</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>3915.7</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.918061556167858</v>
       </c>
       <c r="AF4">
-        <v>1.4</v>
+        <v>3917.618061556168</v>
       </c>
       <c r="AG4">
-        <v>-645</v>
+        <v>3389.118061556168</v>
       </c>
       <c r="AH4">
-        <v>0.001434279274664481</v>
+        <v>0.4853993104225376</v>
       </c>
       <c r="AI4">
-        <v>0.0009828009828009828</v>
+        <v>0.4904613654991069</v>
       </c>
       <c r="AJ4">
-        <v>-1.956323930846223</v>
+        <v>0.4493410513573306</v>
       </c>
       <c r="AK4">
-        <v>-0.82894229533479</v>
+        <v>0.4543590855631408</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>3263.083333333333</v>
+      </c>
+      <c r="AP4">
+        <v>2824.265051296806</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajman Bank PJSC (DFM:AJMANBANK)</t>
+          <t>The National Bank of Ras Al-Khaimah (P.S.C.) (ADX:RAKBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +972,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.04480000000000001</v>
+        <v>0.0659</v>
       </c>
       <c r="E5">
-        <v>0.0222</v>
+        <v>0.136</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,82 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>37.7</v>
+        <v>445.9</v>
       </c>
       <c r="L5">
-        <v>0.306753458096013</v>
+        <v>0.5058997050147492</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>155.1</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05343301064526131</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.347835837631756</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>155.1</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05343301064526131</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.347835837631756</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>394.4</v>
+        <v>645.5</v>
       </c>
       <c r="V5">
-        <v>0.584556099006966</v>
+        <v>0.2223791642264099</v>
       </c>
       <c r="W5">
-        <v>0.05330128658277959</v>
+        <v>0.1893498662363582</v>
       </c>
       <c r="X5">
-        <v>0.06888106922246501</v>
+        <v>0.07589852586086693</v>
       </c>
       <c r="Y5">
-        <v>-0.01557978263968542</v>
+        <v>0.1134513403754913</v>
       </c>
       <c r="Z5">
-        <v>0.5548783240778368</v>
+        <v>0.2028118456476219</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06883605300236548</v>
+        <v>0.05659570933398654</v>
       </c>
       <c r="AC5">
-        <v>-0.06883605300236548</v>
+        <v>-0.05659570933398654</v>
       </c>
       <c r="AD5">
-        <v>1.96</v>
+        <v>2983.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.96</v>
+        <v>2983.5</v>
       </c>
       <c r="AG5">
-        <v>-392.44</v>
+        <v>2338</v>
       </c>
       <c r="AH5">
-        <v>0.002896580261874501</v>
+        <v>0.5068635112636336</v>
       </c>
       <c r="AI5">
-        <v>0.002863571282470853</v>
+        <v>0.5283149171270718</v>
       </c>
       <c r="AJ5">
-        <v>-1.390349323318925</v>
+        <v>0.4461236094414868</v>
       </c>
       <c r="AK5">
-        <v>-1.352961456250431</v>
+        <v>0.4674410700361877</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abu Dhabi Islamic Bank PJSC (ADX:ADIB)</t>
+          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0302</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E6">
-        <v>0.08160000000000001</v>
+        <v>0.0454</v>
+      </c>
+      <c r="F6">
+        <v>0.0308</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1115,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>865.2</v>
+        <v>4044.6</v>
       </c>
       <c r="L6">
-        <v>0.5855837563451777</v>
+        <v>0.6297743798950531</v>
       </c>
       <c r="M6">
-        <v>376.8</v>
+        <v>1736.1</v>
       </c>
       <c r="N6">
-        <v>0.04182809187083024</v>
+        <v>0.04137344292533429</v>
       </c>
       <c r="O6">
-        <v>0.435506241331484</v>
+        <v>0.4292389853137517</v>
       </c>
       <c r="P6">
-        <v>376.8</v>
+        <v>1736.1</v>
       </c>
       <c r="Q6">
-        <v>0.04182809187083024</v>
+        <v>0.04137344292533429</v>
       </c>
       <c r="R6">
-        <v>0.435506241331484</v>
+        <v>0.4292389853137517</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1145,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>881.7</v>
+        <v>61884.1</v>
       </c>
       <c r="V6">
-        <v>0.09787640287290611</v>
+        <v>1.474775807462519</v>
       </c>
       <c r="W6">
-        <v>0.1595632849528798</v>
+        <v>0.132085823454492</v>
       </c>
       <c r="X6">
-        <v>0.06897739734746043</v>
+        <v>0.07668699146952897</v>
       </c>
       <c r="Y6">
-        <v>0.09058588760541934</v>
+        <v>0.05539883198496305</v>
       </c>
       <c r="Z6">
-        <v>0.4356350984785942</v>
+        <v>0.7134382741421258</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06888233085487587</v>
+        <v>0.05710212272706712</v>
       </c>
       <c r="AC6">
-        <v>-0.06888233085487587</v>
+        <v>-0.05710212272706712</v>
       </c>
       <c r="AD6">
-        <v>55.1</v>
+        <v>45235.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>55.1</v>
+        <v>45235.5</v>
       </c>
       <c r="AG6">
-        <v>-826.6</v>
+        <v>-16648.6</v>
       </c>
       <c r="AH6">
-        <v>0.006079396253061765</v>
+        <v>0.5187723917740478</v>
       </c>
       <c r="AI6">
-        <v>0.009468818202127477</v>
+        <v>0.5801691687134072</v>
       </c>
       <c r="AJ6">
-        <v>-0.1010303482161409</v>
+        <v>-0.6577068790468177</v>
       </c>
       <c r="AK6">
-        <v>-0.1674160489326366</v>
+        <v>-1.035013117485421</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,10 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0414</v>
+        <v>0.0522</v>
       </c>
       <c r="E7">
-        <v>0.0563</v>
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="F7">
+        <v>-0.00455</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,28 +1240,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1464</v>
+        <v>1667.5</v>
       </c>
       <c r="L7">
-        <v>0.6588065880658807</v>
+        <v>0.6586223240382336</v>
       </c>
       <c r="M7">
-        <v>601.8</v>
+        <v>700.2</v>
       </c>
       <c r="N7">
-        <v>0.05365788417814631</v>
+        <v>0.06220958642441474</v>
       </c>
       <c r="O7">
-        <v>0.4110655737704918</v>
+        <v>0.4199100449775113</v>
       </c>
       <c r="P7">
-        <v>601.8</v>
+        <v>700.2</v>
       </c>
       <c r="Q7">
-        <v>0.05365788417814631</v>
+        <v>0.06220958642441474</v>
       </c>
       <c r="R7">
-        <v>0.4110655737704918</v>
+        <v>0.4199100449775113</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1249,55 +1270,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1914</v>
+        <v>4767.5</v>
       </c>
       <c r="V7">
-        <v>0.1706566804868263</v>
+        <v>0.4235706987694905</v>
       </c>
       <c r="W7">
-        <v>0.1412186863961261</v>
+        <v>0.1512663739613193</v>
       </c>
       <c r="X7">
-        <v>0.08431413795709661</v>
+        <v>0.0680254477844329</v>
       </c>
       <c r="Y7">
-        <v>0.05690454843902953</v>
+        <v>0.08324092617688644</v>
       </c>
       <c r="Z7">
-        <v>0.2246053083749419</v>
+        <v>0.1697713404412258</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07375200734687898</v>
+        <v>0.05760268942949515</v>
       </c>
       <c r="AC7">
-        <v>-0.07375200734687898</v>
+        <v>-0.05760268942949515</v>
       </c>
       <c r="AD7">
-        <v>5803.4</v>
+        <v>5928.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5803.4</v>
+        <v>5928.8</v>
       </c>
       <c r="AG7">
-        <v>3889.4</v>
+        <v>1161.3</v>
       </c>
       <c r="AH7">
-        <v>0.3409973617566352</v>
+        <v>0.345012598709287</v>
       </c>
       <c r="AI7">
-        <v>0.3306931370090945</v>
+        <v>0.3212797433577006</v>
       </c>
       <c r="AJ7">
-        <v>0.2574926017385087</v>
+        <v>0.09352651246698024</v>
       </c>
       <c r="AK7">
-        <v>0.24875920998772</v>
+        <v>0.08485189460916837</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1314,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Arab Bank P.J.S.C. (ADX:UAB)</t>
+          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1322,6 +1343,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.112</v>
+      </c>
+      <c r="E8">
+        <v>0.106</v>
+      </c>
+      <c r="F8">
+        <v>0.0137</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1335,82 +1365,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>39.3</v>
+        <v>2052.3</v>
       </c>
       <c r="L8">
-        <v>0.3697083725305738</v>
+        <v>0.5754865122539399</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>448</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.02452228079106251</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2182916727573941</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>448</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.02452228079106251</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2182916727573941</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>358.1</v>
+        <v>4372.2</v>
       </c>
       <c r="V8">
-        <v>0.7502618897967736</v>
+        <v>0.2393221340952756</v>
       </c>
       <c r="W8">
-        <v>0.09629992648860572</v>
+        <v>0.1280830296070697</v>
       </c>
       <c r="X8">
-        <v>0.08045719847349594</v>
+        <v>0.0853851955423218</v>
       </c>
       <c r="Y8">
-        <v>0.01584272801510977</v>
+        <v>0.04269783406474795</v>
       </c>
       <c r="Z8">
-        <v>0.4650043744531934</v>
+        <v>0.1010827664399093</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07608463992137077</v>
+        <v>0.05797359985801313</v>
       </c>
       <c r="AC8">
-        <v>-0.07608463992137077</v>
+        <v>-0.05797359985801313</v>
       </c>
       <c r="AD8">
-        <v>185.6</v>
+        <v>29808.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>185.6</v>
+        <v>29808.3</v>
       </c>
       <c r="AG8">
-        <v>-172.5</v>
+        <v>25436.1</v>
       </c>
       <c r="AH8">
-        <v>0.2799818977221301</v>
+        <v>0.6200064895356239</v>
       </c>
       <c r="AI8">
-        <v>0.3301903575876178</v>
+        <v>0.6264050787726719</v>
       </c>
       <c r="AJ8">
-        <v>-0.565944881889764</v>
+        <v>0.5819925317811153</v>
       </c>
       <c r="AK8">
-        <v>-0.8455882352941179</v>
+        <v>0.5886064964907287</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1427,7 +1460,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
+          <t>Mashreqbank PSC (DFM:MASQ)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1436,10 +1469,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.131</v>
+        <v>0.171</v>
       </c>
       <c r="E9">
-        <v>0.127</v>
+        <v>0.263</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1454,28 +1487,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>3885.3</v>
+        <v>1872</v>
       </c>
       <c r="L9">
-        <v>0.6481657574695961</v>
+        <v>0.6541566201907957</v>
       </c>
       <c r="M9">
-        <v>1509.8</v>
+        <v>517</v>
       </c>
       <c r="N9">
-        <v>0.02937188368749623</v>
+        <v>0.06227190055767679</v>
       </c>
       <c r="O9">
-        <v>0.3885929014490515</v>
+        <v>0.2761752136752137</v>
       </c>
       <c r="P9">
-        <v>1509.8</v>
+        <v>517</v>
       </c>
       <c r="Q9">
-        <v>0.02937188368749623</v>
+        <v>0.06227190055767679</v>
       </c>
       <c r="R9">
-        <v>0.3885929014490515</v>
+        <v>0.2761752136752137</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1484,55 +1517,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>66746.10000000001</v>
+        <v>7832.5</v>
       </c>
       <c r="V9">
-        <v>1.298488995757049</v>
+        <v>0.9434132710212834</v>
       </c>
       <c r="W9">
-        <v>0.1306444291262462</v>
+        <v>0.3109996178957686</v>
       </c>
       <c r="X9">
-        <v>0.09809519316842834</v>
+        <v>0.08116774739518684</v>
       </c>
       <c r="Y9">
-        <v>0.0325492359578179</v>
+        <v>0.2298318705005817</v>
       </c>
       <c r="Z9">
-        <v>0.5314661134163212</v>
+        <v>0.3059463735887786</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07691786639627625</v>
+        <v>0.05809720998477561</v>
       </c>
       <c r="AC9">
-        <v>-0.07691786639627625</v>
+        <v>-0.05809720998477561</v>
       </c>
       <c r="AD9">
-        <v>50215.8</v>
+        <v>11317.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>50215.8</v>
+        <v>11317.7</v>
       </c>
       <c r="AG9">
-        <v>-16530.3</v>
+        <v>3485.200000000001</v>
       </c>
       <c r="AH9">
-        <v>0.4941590474981475</v>
+        <v>0.5768450560652396</v>
       </c>
       <c r="AI9">
-        <v>0.6212005190711644</v>
+        <v>0.5979374362713243</v>
       </c>
       <c r="AJ9">
-        <v>-0.4740197174859346</v>
+        <v>0.2956691410392365</v>
       </c>
       <c r="AK9">
-        <v>-1.173143797992989</v>
+        <v>0.3141121545865855</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1549,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC (DFM:EMIRATESNBD)</t>
+          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1558,13 +1591,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.132</v>
+        <v>0.0682</v>
       </c>
       <c r="E10">
-        <v>0.0667</v>
-      </c>
-      <c r="F10">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,28 +1609,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3017.8</v>
+        <v>231.3</v>
       </c>
       <c r="L10">
-        <v>0.4662207047845634</v>
+        <v>0.5494061757719715</v>
       </c>
       <c r="M10">
-        <v>998</v>
+        <v>108.9</v>
       </c>
       <c r="N10">
-        <v>0.04464046089710329</v>
+        <v>0.05087358684480987</v>
       </c>
       <c r="O10">
-        <v>0.3307044867121744</v>
+        <v>0.4708171206225681</v>
       </c>
       <c r="P10">
-        <v>998</v>
+        <v>108.9</v>
       </c>
       <c r="Q10">
-        <v>0.04464046089710329</v>
+        <v>0.05087358684480987</v>
       </c>
       <c r="R10">
-        <v>0.3307044867121744</v>
+        <v>0.4708171206225681</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1609,55 +1639,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>11661.9</v>
+        <v>1259.4</v>
       </c>
       <c r="V10">
-        <v>0.5216358626612513</v>
+        <v>0.5883397178361208</v>
       </c>
       <c r="W10">
-        <v>0.1298604058729367</v>
+        <v>0.1111484863046612</v>
       </c>
       <c r="X10">
-        <v>0.1130293726382527</v>
+        <v>0.07702090871894461</v>
       </c>
       <c r="Y10">
-        <v>0.01683103323468392</v>
+        <v>0.03412757758571662</v>
       </c>
       <c r="Z10">
-        <v>0.1496361333037431</v>
+        <v>0.1394178229625459</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07745868994741489</v>
+        <v>0.05877387076759191</v>
       </c>
       <c r="AC10">
-        <v>-0.07745868994741489</v>
+        <v>-0.05877387076759191</v>
       </c>
       <c r="AD10">
-        <v>32971.5</v>
+        <v>2353.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>32971.5</v>
+        <v>2353.1</v>
       </c>
       <c r="AG10">
-        <v>21309.6</v>
+        <v>1093.7</v>
       </c>
       <c r="AH10">
-        <v>0.595928997847379</v>
+        <v>0.5236442130093242</v>
       </c>
       <c r="AI10">
-        <v>0.5773220967552718</v>
+        <v>0.5194137253603515</v>
       </c>
       <c r="AJ10">
-        <v>0.4880135574588925</v>
+        <v>0.3381566335837739</v>
       </c>
       <c r="AK10">
-        <v>0.4688663386814289</v>
+        <v>0.3343728025925586</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1674,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Commercial Bank of Dubai PSC (DFM:CBD)</t>
+          <t>Emirates Islamic Bank PJSC (DFM:EIB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1683,10 +1713,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0759</v>
+        <v>0.119</v>
       </c>
       <c r="E11">
-        <v>0.122</v>
+        <v>0.163</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1695,103 +1725,94 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.002124695145613879</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.002124695145613879</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>468.6</v>
+        <v>499</v>
       </c>
       <c r="L11">
-        <v>0.6286557552991683</v>
+        <v>0.5034809807284835</v>
       </c>
       <c r="M11">
-        <v>233.5</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.06334780249593054</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.4982927870251814</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>233.5</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.06334780249593054</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.4982927870251814</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>1272</v>
+        <v>352</v>
       </c>
       <c r="V11">
-        <v>0.3450895279435703</v>
+        <v>0.03696741196609921</v>
       </c>
       <c r="W11">
-        <v>0.1296624239070282</v>
+        <v>0.2022617648250983</v>
       </c>
       <c r="X11">
-        <v>0.09443957710704597</v>
+        <v>0.06193691831131753</v>
       </c>
       <c r="Y11">
-        <v>0.03522284679998226</v>
+        <v>0.1403248465137808</v>
       </c>
       <c r="Z11">
-        <v>0.1691733531783833</v>
+        <v>0.614292797818272</v>
       </c>
       <c r="AA11">
-        <v>0.0003594418022653334</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0807963667457938</v>
+        <v>0.05898883088473785</v>
       </c>
       <c r="AC11">
-        <v>-0.08043692494352846</v>
+        <v>-0.05898883088473785</v>
       </c>
       <c r="AD11">
-        <v>3149.8</v>
+        <v>1325.8</v>
       </c>
       <c r="AE11">
-        <v>1.831261192297072</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>3151.631261192297</v>
+        <v>1325.8</v>
       </c>
       <c r="AG11">
-        <v>1879.631261192297</v>
+        <v>973.8</v>
       </c>
       <c r="AH11">
-        <v>0.4609244255506604</v>
+        <v>0.1222194566590153</v>
       </c>
       <c r="AI11">
-        <v>0.4637594931454136</v>
+        <v>0.3089218724514761</v>
       </c>
       <c r="AJ11">
-        <v>0.3377211268555426</v>
+        <v>0.09278085311127415</v>
       </c>
       <c r="AK11">
-        <v>0.3402767340844851</v>
+        <v>0.2471761809274818</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>1615.282051282051</v>
-      </c>
-      <c r="AP11">
-        <v>963.9134672781012</v>
       </c>
     </row>
     <row r="12">
@@ -1802,7 +1823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
+          <t>United Arab Bank P.J.S.C. (ADX:UAB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1811,13 +1832,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.08789999999999999</v>
+        <v>0.0397</v>
       </c>
       <c r="E12">
-        <v>0.0767</v>
-      </c>
-      <c r="F12">
-        <v>0.1</v>
+        <v>0.276</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1832,85 +1850,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>1658.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L12">
-        <v>0.5642840132004218</v>
+        <v>0.4647592463363572</v>
       </c>
       <c r="M12">
-        <v>750.4</v>
+        <v>6.679</v>
       </c>
       <c r="N12">
-        <v>0.04407713498622589</v>
+        <v>0.008811345646437995</v>
       </c>
       <c r="O12">
-        <v>0.4524297600385868</v>
+        <v>0.1002852852852853</v>
       </c>
       <c r="P12">
-        <v>750.4</v>
+        <v>6.04</v>
       </c>
       <c r="Q12">
-        <v>0.04407713498622589</v>
+        <v>0.007968337730870712</v>
       </c>
       <c r="R12">
-        <v>0.4524297600385868</v>
+        <v>0.0906906906906907</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>0.6390000000000002</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.09567300494085944</v>
       </c>
       <c r="U12">
-        <v>6067.1</v>
+        <v>302.5</v>
       </c>
       <c r="V12">
-        <v>0.3563704499932451</v>
+        <v>0.3990765171503958</v>
       </c>
       <c r="W12">
-        <v>0.104749273714791</v>
+        <v>0.1768924302788845</v>
       </c>
       <c r="X12">
-        <v>0.1134093170547064</v>
+        <v>0.06493541789765238</v>
       </c>
       <c r="Y12">
-        <v>-0.008660043339915463</v>
+        <v>0.1119570123812321</v>
       </c>
       <c r="Z12">
-        <v>0.07827175287930231</v>
+        <v>0.7024509803921569</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.08089713314649558</v>
+        <v>0.05928699265882739</v>
       </c>
       <c r="AC12">
-        <v>-0.08089713314649558</v>
+        <v>-0.05928699265882739</v>
       </c>
       <c r="AD12">
-        <v>25323.9</v>
+        <v>250.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>25323.9</v>
+        <v>250.2</v>
       </c>
       <c r="AG12">
-        <v>19256.8</v>
+        <v>-52.30000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.5979867103044728</v>
+        <v>0.2481650466177346</v>
       </c>
       <c r="AI12">
-        <v>0.6124339775959138</v>
+        <v>0.2986036519871106</v>
       </c>
       <c r="AJ12">
-        <v>0.5307608560836791</v>
+        <v>-0.07411081195975629</v>
       </c>
       <c r="AK12">
-        <v>0.545788988875505</v>
+        <v>-0.09768397459843109</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1927,7 +1945,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank Of Sharjah P.J.S.C. (ADX:BOS)</t>
+          <t>Abu Dhabi Islamic Bank PJSC (ADX:ADIB)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1936,10 +1954,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.212</v>
+        <v>0.102</v>
       </c>
       <c r="E13">
-        <v>0.222</v>
+        <v>0.149</v>
+      </c>
+      <c r="F13">
+        <v>0.0669</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1954,82 +1975,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>289.2</v>
+        <v>1284.5</v>
       </c>
       <c r="L13">
-        <v>5.047120418848167</v>
+        <v>0.587925668253387</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>1341.7</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.1340828461500025</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>1.044530945893344</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>591.9</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.0591515514915305</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.4608018684312962</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>749.7999999999998</v>
+      </c>
+      <c r="T13">
+        <v>0.5588432585525825</v>
       </c>
       <c r="U13">
-        <v>722.7</v>
+        <v>440.7</v>
       </c>
       <c r="V13">
-        <v>2.513739130434783</v>
+        <v>0.04404137310748014</v>
       </c>
       <c r="W13">
-        <v>0.2825598436736688</v>
+        <v>0.222972503818914</v>
       </c>
       <c r="X13">
-        <v>0.2359358029161075</v>
+        <v>0.05983496924675391</v>
       </c>
       <c r="Y13">
-        <v>0.04662404075756127</v>
+        <v>0.1631375345721601</v>
       </c>
       <c r="Z13">
-        <v>0.03647126217299981</v>
+        <v>0.4454866137879003</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.08112161852070784</v>
+        <v>0.05971547391944527</v>
       </c>
       <c r="AC13">
-        <v>-0.08112161852070784</v>
+        <v>-0.05971547391944527</v>
       </c>
       <c r="AD13">
-        <v>1602.1</v>
+        <v>54.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1602.1</v>
+        <v>54.6</v>
       </c>
       <c r="AG13">
-        <v>879.3999999999999</v>
+        <v>-386.1</v>
       </c>
       <c r="AH13">
-        <v>0.8478513971210838</v>
+        <v>0.005426841995408056</v>
       </c>
       <c r="AI13">
-        <v>0.8056016493186504</v>
+        <v>0.008054879398096924</v>
       </c>
       <c r="AJ13">
-        <v>0.7536207044305424</v>
+        <v>-0.04013346638393414</v>
       </c>
       <c r="AK13">
-        <v>0.6946287519747234</v>
+        <v>-0.06092019312695257</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2046,7 +2070,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
+          <t>Ajman Bank PJSC (DFM:AJMANBANK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2055,10 +2079,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0659</v>
-      </c>
-      <c r="E14">
-        <v>0.051</v>
+        <v>-0.0246</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2073,85 +2094,82 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>170</v>
+        <v>-10.3</v>
       </c>
       <c r="L14">
-        <v>0.4773939904521202</v>
+        <v>-0.101577909270217</v>
       </c>
       <c r="M14">
-        <v>92.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.05629584352078239</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.5417647058823529</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>92.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.05629584352078239</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.5417647058823529</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>1812.4</v>
+        <v>782.8</v>
       </c>
       <c r="V14">
-        <v>1.107823960880196</v>
+        <v>0.6359574295231131</v>
       </c>
       <c r="W14">
-        <v>0.08101024541339051</v>
+        <v>-0.01509157509157509</v>
       </c>
       <c r="X14">
-        <v>0.1173562476891574</v>
+        <v>0.05978370222424673</v>
       </c>
       <c r="Y14">
-        <v>-0.03634600227576691</v>
+        <v>-0.07487527731582182</v>
       </c>
       <c r="Z14">
-        <v>0.1698140200286123</v>
+        <v>0.3495828449286354</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.08254231941054127</v>
+        <v>0.05973562041364591</v>
       </c>
       <c r="AC14">
-        <v>-0.08254231941054127</v>
+        <v>-0.05973562041364591</v>
       </c>
       <c r="AD14">
-        <v>2648.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2648.8</v>
+        <v>2.7</v>
       </c>
       <c r="AG14">
-        <v>836.4000000000001</v>
+        <v>-780.0999999999999</v>
       </c>
       <c r="AH14">
-        <v>0.6181852128454071</v>
+        <v>0.002188715953307393</v>
       </c>
       <c r="AI14">
-        <v>0.5600236796481881</v>
+        <v>0.00330760749724366</v>
       </c>
       <c r="AJ14">
-        <v>0.3382947743083644</v>
+        <v>-1.730479148181011</v>
       </c>
       <c r="AK14">
-        <v>0.286693631315555</v>
+        <v>-23.28656716417902</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2168,7 +2186,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mashreqbank PSC (DFM:MASQ)</t>
+          <t>National Bank of Umm Al-Qaiwain (PSC) (ADX:NBQ)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2177,10 +2195,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.06559999999999999</v>
+        <v>0.0268</v>
       </c>
       <c r="E15">
-        <v>0.0953</v>
+        <v>0.0315</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2195,28 +2213,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>903.1</v>
+        <v>133.4</v>
       </c>
       <c r="L15">
-        <v>0.5249055507120023</v>
+        <v>0.7460850111856823</v>
       </c>
       <c r="M15">
-        <v>63.5</v>
+        <v>54.4</v>
       </c>
       <c r="N15">
-        <v>0.01192376302694583</v>
+        <v>0.05708289611752361</v>
       </c>
       <c r="O15">
-        <v>0.07031336507584984</v>
+        <v>0.4077961019490254</v>
       </c>
       <c r="P15">
-        <v>63.5</v>
+        <v>54.4</v>
       </c>
       <c r="Q15">
-        <v>0.01192376302694583</v>
+        <v>0.05708289611752361</v>
       </c>
       <c r="R15">
-        <v>0.07031336507584984</v>
+        <v>0.4077961019490254</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2225,55 +2243,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>6810.8</v>
+        <v>1248</v>
       </c>
       <c r="V15">
-        <v>1.278903389353112</v>
+        <v>1.309548793284365</v>
       </c>
       <c r="W15">
-        <v>0.1710935131858139</v>
+        <v>0.09373902044831707</v>
       </c>
       <c r="X15">
-        <v>0.1259325136821891</v>
+        <v>0.05976526302093987</v>
       </c>
       <c r="Y15">
-        <v>0.04516099950362476</v>
+        <v>0.0339737574273772</v>
       </c>
       <c r="Z15">
-        <v>0.2024355806565478</v>
+        <v>0.2297905153579232</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.08337812204254386</v>
+        <v>0.05974733999085622</v>
       </c>
       <c r="AC15">
-        <v>-0.08337812204254386</v>
+        <v>-0.05974733999085622</v>
       </c>
       <c r="AD15">
-        <v>10145.1</v>
+        <v>0.972</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>10145.1</v>
+        <v>0.972</v>
       </c>
       <c r="AG15">
-        <v>3334.3</v>
+        <v>-1247.028</v>
       </c>
       <c r="AH15">
-        <v>0.655766421470402</v>
+        <v>0.001018897829286394</v>
       </c>
       <c r="AI15">
-        <v>0.618607430533113</v>
+        <v>0.0006444460946036258</v>
       </c>
       <c r="AJ15">
-        <v>0.3850319868819142</v>
+        <v>4.24118791407621</v>
       </c>
       <c r="AK15">
-        <v>0.34771772116257</v>
+        <v>-4.791249154730437</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2290,7 +2308,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al-Khaimah (P.S.C.) (ADX:RAKBANK)</t>
+          <t>Bank Of Sharjah P.J.S.C. (ADX:BOS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2299,10 +2317,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.03759999999999999</v>
+        <v>-0.175</v>
       </c>
       <c r="E16">
-        <v>0.09320000000000001</v>
+        <v>-0.5539999999999999</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2317,85 +2335,82 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>301.6</v>
+        <v>1.48</v>
       </c>
       <c r="L16">
-        <v>0.4283482459877859</v>
+        <v>0.02301710730948678</v>
       </c>
       <c r="M16">
-        <v>102.7</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.04788102009417688</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.3405172413793103</v>
+        <v>-0</v>
       </c>
       <c r="P16">
-        <v>102.7</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.04788102009417688</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.3405172413793103</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>1384.8</v>
+        <v>907.6</v>
       </c>
       <c r="V16">
-        <v>0.6456245046389109</v>
+        <v>1.696448598130841</v>
       </c>
       <c r="W16">
-        <v>0.136612764415455</v>
+        <v>0.003847153626202236</v>
       </c>
       <c r="X16">
-        <v>0.1166340497423925</v>
+        <v>0.113992100875517</v>
       </c>
       <c r="Y16">
-        <v>0.01997871467306249</v>
+        <v>-0.1101449472493148</v>
       </c>
       <c r="Z16">
-        <v>0.1934181248798176</v>
+        <v>0.05086622893758405</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.0847991705767288</v>
+        <v>0.0598570940690514</v>
       </c>
       <c r="AC16">
-        <v>-0.0847991705767288</v>
+        <v>-0.0598570940690514</v>
       </c>
       <c r="AD16">
-        <v>3421.1</v>
+        <v>1847</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>3421.1</v>
+        <v>1847</v>
       </c>
       <c r="AG16">
-        <v>2036.3</v>
+        <v>939.4</v>
       </c>
       <c r="AH16">
-        <v>0.6146424721523536</v>
+        <v>0.7753988245172124</v>
       </c>
       <c r="AI16">
-        <v>0.5914969397282064</v>
+        <v>0.6475930016479086</v>
       </c>
       <c r="AJ16">
-        <v>0.4870132976179087</v>
+        <v>0.6371405317417254</v>
       </c>
       <c r="AK16">
-        <v>0.4629006592407365</v>
+        <v>0.483106196965801</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.119</v>
+        <v>0.1012</v>
       </c>
       <c r="E2">
         <v>0.128</v>
       </c>
       <c r="F2">
-        <v>0.0183</v>
+        <v>-0.0127</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3.900331130699694E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>3.456690493199051E-05</v>
       </c>
       <c r="K2">
-        <v>9969.9</v>
+        <v>22335.43</v>
       </c>
       <c r="L2">
-        <v>0.6093437723463944</v>
+        <v>0.5850892220964835</v>
       </c>
       <c r="M2">
-        <v>4834.099999999999</v>
+        <v>9546.16</v>
       </c>
       <c r="N2">
-        <v>0.06161660580336373</v>
+        <v>0.0565860332172112</v>
       </c>
       <c r="O2">
-        <v>0.484869457065768</v>
+        <v>0.4273998754445292</v>
       </c>
       <c r="P2">
-        <v>4834.099999999999</v>
+        <v>9522.85</v>
       </c>
       <c r="Q2">
-        <v>0.06161660580336373</v>
+        <v>0.05644786033572868</v>
       </c>
       <c r="R2">
-        <v>0.484869457065768</v>
+        <v>0.4263562420781691</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>23.31</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002441819537908437</v>
       </c>
       <c r="U2">
-        <v>32342.7</v>
+        <v>56328.7</v>
       </c>
       <c r="V2">
-        <v>0.4122478634112766</v>
+        <v>0.3338952719504308</v>
       </c>
       <c r="W2">
-        <v>0.1403821827315004</v>
+        <v>0.1414147361982247</v>
       </c>
       <c r="X2">
-        <v>0.0820645343037899</v>
+        <v>0.07677746778972311</v>
       </c>
       <c r="Y2">
-        <v>0.05831764842771053</v>
+        <v>0.06463726840850162</v>
       </c>
       <c r="Z2">
-        <v>0.2303741219307175</v>
+        <v>0.2415384028848523</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06175997312434371</v>
+        <v>0.06288476902054202</v>
       </c>
       <c r="AC2">
-        <v>-0.06175997312434371</v>
+        <v>-0.06288476902054202</v>
       </c>
       <c r="AD2">
-        <v>96169.5</v>
+        <v>152390.706</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2.705359964210879</v>
       </c>
       <c r="AF2">
-        <v>96169.5</v>
+        <v>152393.4113599642</v>
       </c>
       <c r="AG2">
-        <v>63826.8</v>
+        <v>96064.71135996419</v>
       </c>
       <c r="AH2">
-        <v>0.5507232682792743</v>
+        <v>0.4746052056492486</v>
       </c>
       <c r="AI2">
-        <v>0.5809747159600632</v>
+        <v>0.5208693612098463</v>
       </c>
       <c r="AJ2">
-        <v>0.4485958449915766</v>
+        <v>0.3628281656518698</v>
       </c>
       <c r="AK2">
-        <v>0.4792211946067456</v>
+        <v>0.4066292935709072</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>75069.31330049262</v>
+      </c>
+      <c r="AP2">
+        <v>47322.51791131241</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
+          <t>Emirates NBD Bank PJSC (DFM:EMIRATESNBD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0834</v>
+        <v>0.152</v>
       </c>
       <c r="E3">
-        <v>0.0641</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F3">
-        <v>-0.0127</v>
+        <v>-0.0159</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4594.4</v>
+        <v>6264.4</v>
       </c>
       <c r="L3">
-        <v>0.6179421654337592</v>
+        <v>0.5403792074254266</v>
       </c>
       <c r="M3">
-        <v>2333.6</v>
+        <v>2200.7</v>
       </c>
       <c r="N3">
-        <v>0.05649993826069483</v>
+        <v>0.05965880595639244</v>
       </c>
       <c r="O3">
-        <v>0.5079226884903361</v>
+        <v>0.3513025988123364</v>
       </c>
       <c r="P3">
-        <v>2333.6</v>
+        <v>2200.7</v>
       </c>
       <c r="Q3">
-        <v>0.05649993826069483</v>
+        <v>0.05965880595639244</v>
       </c>
       <c r="R3">
-        <v>0.5079226884903361</v>
+        <v>0.3513025988123364</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>20690.9</v>
+        <v>14992.5</v>
       </c>
       <c r="V3">
-        <v>0.500957564517574</v>
+        <v>0.4064318845372898</v>
       </c>
       <c r="W3">
-        <v>0.1403821827315004</v>
+        <v>0.2188620181255372</v>
       </c>
       <c r="X3">
-        <v>0.0820645343037899</v>
+        <v>0.0800065940919531</v>
       </c>
       <c r="Y3">
-        <v>0.05831764842771053</v>
+        <v>0.1388554240335841</v>
       </c>
       <c r="Z3">
-        <v>0.6764994904644049</v>
+        <v>0.2386089276121201</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06150290055385498</v>
+        <v>0.06136515935448803</v>
       </c>
       <c r="AC3">
-        <v>-0.06150290055385498</v>
+        <v>-0.06136515935448803</v>
       </c>
       <c r="AD3">
-        <v>46569.6</v>
+        <v>36483</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>46569.6</v>
+        <v>36483</v>
       </c>
       <c r="AG3">
-        <v>25878.7</v>
+        <v>21490.5</v>
       </c>
       <c r="AH3">
-        <v>0.5299690573707528</v>
+        <v>0.4972393762666772</v>
       </c>
       <c r="AI3">
-        <v>0.5699947859165894</v>
+        <v>0.5206368143300348</v>
       </c>
       <c r="AJ3">
-        <v>0.3852063219879312</v>
+        <v>0.3681229080519232</v>
       </c>
       <c r="AK3">
-        <v>0.4241651901545461</v>
+        <v>0.3901596367551238</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
+          <t>The National Bank of Ras Al-Khaimah (P.S.C.) (ADX:RAKBANK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.122</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E4">
-        <v>0.128</v>
-      </c>
-      <c r="F4">
-        <v>0.0493</v>
+        <v>0.144</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2532.2</v>
+        <v>576.9</v>
       </c>
       <c r="L4">
-        <v>0.5759974523452072</v>
+        <v>0.543015813253012</v>
       </c>
       <c r="M4">
-        <v>1272.6</v>
+        <v>169.8</v>
       </c>
       <c r="N4">
-        <v>0.06129792061037816</v>
+        <v>0.05124954726548352</v>
       </c>
       <c r="O4">
-        <v>0.5025669378406129</v>
+        <v>0.2943317732709309</v>
       </c>
       <c r="P4">
-        <v>1272.6</v>
+        <v>169.8</v>
       </c>
       <c r="Q4">
-        <v>0.06129792061037816</v>
+        <v>0.05124954726548352</v>
       </c>
       <c r="R4">
-        <v>0.5025669378406129</v>
+        <v>0.2943317732709309</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1802.9</v>
+        <v>215.5</v>
       </c>
       <c r="V4">
-        <v>0.08684112923813515</v>
+        <v>0.06504285886756006</v>
       </c>
       <c r="W4">
-        <v>0.142447289664949</v>
+        <v>0.2171817942250499</v>
       </c>
       <c r="X4">
-        <v>0.08782296224055908</v>
+        <v>0.07914674120388435</v>
       </c>
       <c r="Y4">
-        <v>0.05462432742438994</v>
+        <v>0.1380350530211655</v>
       </c>
       <c r="Z4">
-        <v>0.1017344518368528</v>
+        <v>0.2127225036541658</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06163813916158566</v>
+        <v>0.06148971016169683</v>
       </c>
       <c r="AC4">
-        <v>-0.06163813916158566</v>
+        <v>-0.06148971016169683</v>
       </c>
       <c r="AD4">
-        <v>31520.8</v>
+        <v>3083.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>31520.8</v>
+        <v>3083.4</v>
       </c>
       <c r="AG4">
-        <v>29717.9</v>
+        <v>2867.9</v>
       </c>
       <c r="AH4">
-        <v>0.6029031190646058</v>
+        <v>0.4820373323328018</v>
       </c>
       <c r="AI4">
-        <v>0.6110790156294226</v>
+        <v>0.4948721652462805</v>
       </c>
       <c r="AJ4">
-        <v>0.5887204133220282</v>
+        <v>0.4639789034314281</v>
       </c>
       <c r="AK4">
-        <v>0.5969931276655155</v>
+        <v>0.4767755020614443</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
+          <t>First Abu Dhabi Bank P.J.S.C. (ADX:FAB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +966,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.119</v>
+        <v>0.0834</v>
       </c>
       <c r="E5">
-        <v>0.133</v>
+        <v>0.0641</v>
+      </c>
+      <c r="F5">
+        <v>-0.0127</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>268.6</v>
+        <v>4594.4</v>
       </c>
       <c r="L5">
-        <v>0.4865942028985508</v>
+        <v>0.6179421654337592</v>
       </c>
       <c r="M5">
-        <v>113.1</v>
+        <v>2333.6</v>
       </c>
       <c r="N5">
-        <v>0.05156143150216549</v>
+        <v>0.05649993826069483</v>
       </c>
       <c r="O5">
-        <v>0.4210722263588979</v>
+        <v>0.5079226884903361</v>
       </c>
       <c r="P5">
-        <v>113.1</v>
+        <v>2333.6</v>
       </c>
       <c r="Q5">
-        <v>0.05156143150216549</v>
+        <v>0.05649993826069483</v>
       </c>
       <c r="R5">
-        <v>0.4210722263588979</v>
+        <v>0.5079226884903361</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1017,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1831.5</v>
+        <v>20690.9</v>
       </c>
       <c r="V5">
-        <v>0.8349669478003191</v>
+        <v>0.500957564517574</v>
       </c>
       <c r="W5">
-        <v>0.1233694653683631</v>
+        <v>0.1403821827315004</v>
       </c>
       <c r="X5">
-        <v>0.09433808610743349</v>
+        <v>0.08204662127734649</v>
       </c>
       <c r="Y5">
-        <v>0.02903137926092957</v>
+        <v>0.05833556145415394</v>
       </c>
       <c r="Z5">
-        <v>0.1687608914977529</v>
+        <v>0.6764994904644049</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06175997312434371</v>
+        <v>0.06149448087715044</v>
       </c>
       <c r="AC5">
-        <v>-0.06175997312434371</v>
+        <v>-0.06149448087715044</v>
       </c>
       <c r="AD5">
-        <v>4300.1</v>
+        <v>46569.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4300.1</v>
+        <v>46569.6</v>
       </c>
       <c r="AG5">
-        <v>2468.6</v>
+        <v>25878.7</v>
       </c>
       <c r="AH5">
-        <v>0.6622058642355551</v>
+        <v>0.5299690573707528</v>
       </c>
       <c r="AI5">
-        <v>0.6449827508624569</v>
+        <v>0.5699947859165894</v>
       </c>
       <c r="AJ5">
-        <v>0.5295038716458249</v>
+        <v>0.3852063219879312</v>
       </c>
       <c r="AK5">
-        <v>0.5105159755971462</v>
+        <v>0.4241651901545461</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mashreqbank PSC (DFM:MASQ)</t>
+          <t>Abu Dhabi Commercial Bank PJSC (ADX:ADCB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1091,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.219</v>
+        <v>0.122</v>
       </c>
       <c r="E6">
-        <v>0.329</v>
+        <v>0.128</v>
+      </c>
+      <c r="F6">
+        <v>0.0493</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1112,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2339.9</v>
+        <v>2532.2</v>
       </c>
       <c r="L6">
-        <v>0.6644234318652924</v>
+        <v>0.5759974523452072</v>
       </c>
       <c r="M6">
-        <v>1035.8</v>
+        <v>1272.6</v>
       </c>
       <c r="N6">
-        <v>0.08699376816219576</v>
+        <v>0.06129792061037816</v>
       </c>
       <c r="O6">
-        <v>0.4426684901064148</v>
+        <v>0.5025669378406129</v>
       </c>
       <c r="P6">
-        <v>1035.8</v>
+        <v>1272.6</v>
       </c>
       <c r="Q6">
-        <v>0.08699376816219576</v>
+        <v>0.06129792061037816</v>
       </c>
       <c r="R6">
-        <v>0.4426684901064148</v>
+        <v>0.5025669378406129</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1142,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>7908.9</v>
+        <v>1802.9</v>
       </c>
       <c r="V6">
-        <v>0.6642450405657366</v>
+        <v>0.08684112923813515</v>
       </c>
       <c r="W6">
-        <v>0.3185444347636681</v>
+        <v>0.142447289664949</v>
       </c>
       <c r="X6">
-        <v>0.08053287473042292</v>
+        <v>0.08780220481327378</v>
       </c>
       <c r="Y6">
-        <v>0.2380115600332451</v>
+        <v>0.05464508485167524</v>
       </c>
       <c r="Z6">
-        <v>0.3251560364885326</v>
+        <v>0.1017344518368528</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06225170345459567</v>
+        <v>0.06162989645195442</v>
       </c>
       <c r="AC6">
-        <v>-0.06225170345459567</v>
+        <v>-0.06162989645195442</v>
       </c>
       <c r="AD6">
-        <v>12187.4</v>
+        <v>31520.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12187.4</v>
+        <v>31520.8</v>
       </c>
       <c r="AG6">
-        <v>4278.5</v>
+        <v>29717.9</v>
       </c>
       <c r="AH6">
-        <v>0.5058271768905122</v>
+        <v>0.6029031190646058</v>
       </c>
       <c r="AI6">
-        <v>0.5591114699648588</v>
+        <v>0.6110790156294226</v>
       </c>
       <c r="AJ6">
-        <v>0.2643480732278454</v>
+        <v>0.5887204133220282</v>
       </c>
       <c r="AK6">
-        <v>0.3080517535585972</v>
+        <v>0.5969931276655155</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,117 +1207,1456 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Sharjah Islamic Bank PJSC (ADX:SIB)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.119</v>
+      </c>
+      <c r="E7">
+        <v>0.133</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>268.6</v>
+      </c>
+      <c r="L7">
+        <v>0.4865942028985508</v>
+      </c>
+      <c r="M7">
+        <v>113.1</v>
+      </c>
+      <c r="N7">
+        <v>0.05156143150216549</v>
+      </c>
+      <c r="O7">
+        <v>0.4210722263588979</v>
+      </c>
+      <c r="P7">
+        <v>113.1</v>
+      </c>
+      <c r="Q7">
+        <v>0.05156143150216549</v>
+      </c>
+      <c r="R7">
+        <v>0.4210722263588979</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1831.5</v>
+      </c>
+      <c r="V7">
+        <v>0.8349669478003191</v>
+      </c>
+      <c r="W7">
+        <v>0.1233694653683631</v>
+      </c>
+      <c r="X7">
+        <v>0.09431411050601883</v>
+      </c>
+      <c r="Y7">
+        <v>0.02905535486234423</v>
+      </c>
+      <c r="Z7">
+        <v>0.1687608914977529</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06175187430678441</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06175187430678441</v>
+      </c>
+      <c r="AD7">
+        <v>4300.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>4300.1</v>
+      </c>
+      <c r="AG7">
+        <v>2468.6</v>
+      </c>
+      <c r="AH7">
+        <v>0.6622058642355551</v>
+      </c>
+      <c r="AI7">
+        <v>0.6449827508624569</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5295038716458249</v>
+      </c>
+      <c r="AK7">
+        <v>0.5105159755971462</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mashreqbank PSC (DFM:MASQ)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.219</v>
+      </c>
+      <c r="E8">
+        <v>0.329</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>2339.9</v>
+      </c>
+      <c r="L8">
+        <v>0.6644234318652924</v>
+      </c>
+      <c r="M8">
+        <v>1035.8</v>
+      </c>
+      <c r="N8">
+        <v>0.08699376816219576</v>
+      </c>
+      <c r="O8">
+        <v>0.4426684901064148</v>
+      </c>
+      <c r="P8">
+        <v>1035.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.08699376816219576</v>
+      </c>
+      <c r="R8">
+        <v>0.4426684901064148</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>7908.9</v>
+      </c>
+      <c r="V8">
+        <v>0.6642450405657366</v>
+      </c>
+      <c r="W8">
+        <v>0.3185444347636681</v>
+      </c>
+      <c r="X8">
+        <v>0.08051571827397183</v>
+      </c>
+      <c r="Y8">
+        <v>0.2380287164896962</v>
+      </c>
+      <c r="Z8">
+        <v>0.3251560364885326</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06224322520007668</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06224322520007668</v>
+      </c>
+      <c r="AD8">
+        <v>12187.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>12187.4</v>
+      </c>
+      <c r="AG8">
+        <v>4278.5</v>
+      </c>
+      <c r="AH8">
+        <v>0.5058271768905122</v>
+      </c>
+      <c r="AI8">
+        <v>0.5591114699648588</v>
+      </c>
+      <c r="AJ8">
+        <v>0.2643480732278454</v>
+      </c>
+      <c r="AK8">
+        <v>0.3080517535585972</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai Islamic Bank P.J.S.C. (DFM:DIB)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0805</v>
+      </c>
+      <c r="E9">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="F9">
+        <v>-0.0239</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>2014.7</v>
+      </c>
+      <c r="L9">
+        <v>0.6434890925931841</v>
+      </c>
+      <c r="M9">
+        <v>1021.6</v>
+      </c>
+      <c r="N9">
+        <v>0.0732303501666607</v>
+      </c>
+      <c r="O9">
+        <v>0.5070730133518638</v>
+      </c>
+      <c r="P9">
+        <v>1021.6</v>
+      </c>
+      <c r="Q9">
+        <v>0.0732303501666607</v>
+      </c>
+      <c r="R9">
+        <v>0.5070730133518638</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>2335.6</v>
+      </c>
+      <c r="V9">
+        <v>0.1674205225619153</v>
+      </c>
+      <c r="W9">
+        <v>0.1712685108046993</v>
+      </c>
+      <c r="X9">
+        <v>0.07270830906921616</v>
+      </c>
+      <c r="Y9">
+        <v>0.09856020173548316</v>
+      </c>
+      <c r="Z9">
+        <v>0.2422415994181683</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06273173187719669</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06273173187719669</v>
+      </c>
+      <c r="AD9">
+        <v>6884.9</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>6884.9</v>
+      </c>
+      <c r="AG9">
+        <v>4549.299999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.3304424201119249</v>
+      </c>
+      <c r="AI9">
+        <v>0.3405870946039535</v>
+      </c>
+      <c r="AJ9">
+        <v>0.2459107666028822</v>
+      </c>
+      <c r="AK9">
+        <v>0.2544465076737214</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bank Of Sharjah P.J.S.C. (ADX:BOS)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0693</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>39.3</v>
+      </c>
+      <c r="L10">
+        <v>0.2689938398357289</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1120.2</v>
+      </c>
+      <c r="V10">
+        <v>1.49399839957322</v>
+      </c>
+      <c r="W10">
+        <v>0.03912004778021103</v>
+      </c>
+      <c r="X10">
+        <v>0.09866738186401243</v>
+      </c>
+      <c r="Y10">
+        <v>-0.0595473340838014</v>
+      </c>
+      <c r="Z10">
+        <v>0.07515432098765432</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06288027205989391</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06288027205989391</v>
+      </c>
+      <c r="AD10">
+        <v>1691.5</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1691.5</v>
+      </c>
+      <c r="AG10">
+        <v>571.3</v>
+      </c>
+      <c r="AH10">
+        <v>0.6928685536394543</v>
+      </c>
+      <c r="AI10">
+        <v>0.6230891074520205</v>
+      </c>
+      <c r="AJ10">
+        <v>0.4324426614185149</v>
+      </c>
+      <c r="AK10">
+        <v>0.358294136092819</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>United Arab Bank P.J.S.C. (ADX:UAB)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.199</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L11">
+        <v>0.4478371501272265</v>
+      </c>
+      <c r="M11">
+        <v>13.71</v>
+      </c>
+      <c r="N11">
+        <v>0.01782139607435331</v>
+      </c>
+      <c r="O11">
+        <v>0.1947443181818181</v>
+      </c>
+      <c r="P11">
+        <v>12.1</v>
+      </c>
+      <c r="Q11">
+        <v>0.01572858442740153</v>
+      </c>
+      <c r="R11">
+        <v>0.171875</v>
+      </c>
+      <c r="S11">
+        <v>1.609999999999999</v>
+      </c>
+      <c r="T11">
+        <v>0.1174325309992706</v>
+      </c>
+      <c r="U11">
+        <v>346.9</v>
+      </c>
+      <c r="V11">
+        <v>0.4509294163525283</v>
+      </c>
+      <c r="W11">
+        <v>0.1197890079972775</v>
+      </c>
+      <c r="X11">
+        <v>0.07788227410665817</v>
+      </c>
+      <c r="Y11">
+        <v>0.04190673389061936</v>
+      </c>
+      <c r="Z11">
+        <v>0.2936122525214792</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06288926598119013</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06288926598119013</v>
+      </c>
+      <c r="AD11">
+        <v>649.9</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>649.9</v>
+      </c>
+      <c r="AG11">
+        <v>303</v>
+      </c>
+      <c r="AH11">
+        <v>0.4579340473506201</v>
+      </c>
+      <c r="AI11">
+        <v>0.4808375258952353</v>
+      </c>
+      <c r="AJ11">
+        <v>0.2825701762566446</v>
+      </c>
+      <c r="AK11">
+        <v>0.3015825619587937</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Commercial Bank of Dubai PSC (DFM:CBD)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.149</v>
+      </c>
+      <c r="E12">
+        <v>0.163</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0.001207663238833501</v>
+      </c>
+      <c r="J12">
+        <v>0.001124115091376187</v>
+      </c>
+      <c r="K12">
+        <v>801.9</v>
+      </c>
+      <c r="L12">
+        <v>0.6504177143320625</v>
+      </c>
+      <c r="M12">
+        <v>396.7</v>
+      </c>
+      <c r="N12">
+        <v>0.06798046439893754</v>
+      </c>
+      <c r="O12">
+        <v>0.4947000872926799</v>
+      </c>
+      <c r="P12">
+        <v>396.7</v>
+      </c>
+      <c r="Q12">
+        <v>0.06798046439893754</v>
+      </c>
+      <c r="R12">
+        <v>0.4947000872926799</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>742.6</v>
+      </c>
+      <c r="V12">
+        <v>0.1272555907805672</v>
+      </c>
+      <c r="W12">
+        <v>0.197027027027027</v>
+      </c>
+      <c r="X12">
+        <v>0.07399293862605012</v>
+      </c>
+      <c r="Y12">
+        <v>0.1230340884009769</v>
+      </c>
+      <c r="Z12">
+        <v>0.1652701931872652</v>
+      </c>
+      <c r="AA12">
+        <v>0.0001857827183164626</v>
+      </c>
+      <c r="AB12">
+        <v>0.06339344751633624</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06320766479801979</v>
+      </c>
+      <c r="AD12">
+        <v>3386.2</v>
+      </c>
+      <c r="AE12">
+        <v>2.705359964210879</v>
+      </c>
+      <c r="AF12">
+        <v>3388.905359964211</v>
+      </c>
+      <c r="AG12">
+        <v>2646.305359964211</v>
+      </c>
+      <c r="AH12">
+        <v>0.3673846961098162</v>
+      </c>
+      <c r="AI12">
+        <v>0.426014541545653</v>
+      </c>
+      <c r="AJ12">
+        <v>0.3119978881448155</v>
+      </c>
+      <c r="AK12">
+        <v>0.3669153242809096</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>1668.07881773399</v>
+      </c>
+      <c r="AP12">
+        <v>1303.598699489759</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>National Bank of Fujairah PJSC (ADX:NBF)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D13">
         <v>0.0644</v>
       </c>
-      <c r="E7">
+      <c r="E13">
         <v>0.0534</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>234.8</v>
       </c>
-      <c r="L7">
+      <c r="L13">
         <v>0.5140105078809107</v>
       </c>
-      <c r="M7">
+      <c r="M13">
         <v>79</v>
       </c>
-      <c r="N7">
+      <c r="N13">
         <v>0.03448576916361096</v>
       </c>
-      <c r="O7">
+      <c r="O13">
         <v>0.3364565587734242</v>
       </c>
-      <c r="P7">
+      <c r="P13">
         <v>79</v>
       </c>
-      <c r="Q7">
+      <c r="Q13">
         <v>0.03448576916361096</v>
       </c>
-      <c r="R7">
+      <c r="R13">
         <v>0.3364565587734242</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>108.5</v>
       </c>
-      <c r="V7">
+      <c r="V13">
         <v>0.04736336650951632</v>
       </c>
-      <c r="W7">
+      <c r="W13">
         <v>0.136432306798373</v>
       </c>
-      <c r="X7">
-        <v>0.07568742449775531</v>
-      </c>
-      <c r="Y7">
-        <v>0.06074488230061773</v>
-      </c>
-      <c r="Z7">
+      <c r="X13">
+        <v>0.07567266147278803</v>
+      </c>
+      <c r="Y13">
+        <v>0.060759645325585</v>
+      </c>
+      <c r="Z13">
         <v>0.1680833057364683</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.06350334988381537</v>
-      </c>
-      <c r="AC7">
-        <v>-0.06350334988381537</v>
-      </c>
-      <c r="AD7">
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06349463899941524</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06349463899941524</v>
+      </c>
+      <c r="AD13">
         <v>1591.6</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
         <v>1591.6</v>
       </c>
-      <c r="AG7">
+      <c r="AG13">
         <v>1483.1</v>
       </c>
-      <c r="AH7">
+      <c r="AH13">
         <v>0.409952606635071</v>
       </c>
-      <c r="AI7">
+      <c r="AI13">
         <v>0.4207799074686054</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ13">
         <v>0.3929886854447653</v>
       </c>
-      <c r="AK7">
+      <c r="AK13">
         <v>0.4036744692433315</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank PJSC (DFM:EIB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.154</v>
+      </c>
+      <c r="E14">
+        <v>0.198</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>809.3</v>
+      </c>
+      <c r="L14">
+        <v>0.6228738551527746</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>383.3</v>
+      </c>
+      <c r="V14">
+        <v>0.03131101072563451</v>
+      </c>
+      <c r="W14">
+        <v>0.2728682693280285</v>
+      </c>
+      <c r="X14">
+        <v>0.06964245841006124</v>
+      </c>
+      <c r="Y14">
+        <v>0.2032258109179673</v>
+      </c>
+      <c r="Z14">
+        <v>0.3297966850267787</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.064202852853604</v>
+      </c>
+      <c r="AC14">
+        <v>-0.064202852853604</v>
+      </c>
+      <c r="AD14">
+        <v>3493.5</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>3493.5</v>
+      </c>
+      <c r="AG14">
+        <v>3110.2</v>
+      </c>
+      <c r="AH14">
+        <v>0.2220181503889369</v>
+      </c>
+      <c r="AI14">
+        <v>0.4761028660206877</v>
+      </c>
+      <c r="AJ14">
+        <v>0.2025938157491906</v>
+      </c>
+      <c r="AK14">
+        <v>0.4472276544346026</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Islamic Bank PJSC (ADX:ADIB)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.131</v>
+      </c>
+      <c r="E15">
+        <v>0.175</v>
+      </c>
+      <c r="F15">
+        <v>0.0343</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1580.8</v>
+      </c>
+      <c r="L15">
+        <v>0.5831919132295432</v>
+      </c>
+      <c r="M15">
+        <v>802.4</v>
+      </c>
+      <c r="N15">
+        <v>0.05871634822950891</v>
+      </c>
+      <c r="O15">
+        <v>0.5075910931174089</v>
+      </c>
+      <c r="P15">
+        <v>802.4</v>
+      </c>
+      <c r="Q15">
+        <v>0.05871634822950891</v>
+      </c>
+      <c r="R15">
+        <v>0.5075910931174089</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>1080</v>
+      </c>
+      <c r="V15">
+        <v>0.07902998016932905</v>
+      </c>
+      <c r="W15">
+        <v>0.2452183355309082</v>
+      </c>
+      <c r="X15">
+        <v>0.06602291680794434</v>
+      </c>
+      <c r="Y15">
+        <v>0.1791954187229639</v>
+      </c>
+      <c r="Z15">
+        <v>0.4522792498164586</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.06512667264475894</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06512667264475894</v>
+      </c>
+      <c r="AD15">
+        <v>541.7</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>541.7</v>
+      </c>
+      <c r="AG15">
+        <v>-538.3</v>
+      </c>
+      <c r="AH15">
+        <v>0.03812801779354421</v>
+      </c>
+      <c r="AI15">
+        <v>0.06848120148668808</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.04100583512348217</v>
+      </c>
+      <c r="AK15">
+        <v>-0.07881174782583233</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Commercial Bank International P.S.C. (ADX:CBI)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0268</v>
+      </c>
+      <c r="E16">
+        <v>0.102</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>70.7</v>
+      </c>
+      <c r="L16">
+        <v>0.3963004484304933</v>
+      </c>
+      <c r="M16">
+        <v>3.75</v>
+      </c>
+      <c r="N16">
+        <v>0.009788566953797963</v>
+      </c>
+      <c r="O16">
+        <v>0.05304101838755304</v>
+      </c>
+      <c r="P16">
+        <v>3.75</v>
+      </c>
+      <c r="Q16">
+        <v>0.009788566953797963</v>
+      </c>
+      <c r="R16">
+        <v>0.05304101838755304</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>517.4</v>
+      </c>
+      <c r="V16">
+        <v>1.350561211172018</v>
+      </c>
+      <c r="W16">
+        <v>0.09537299338999057</v>
+      </c>
+      <c r="X16">
+        <v>0.06554517214937697</v>
+      </c>
+      <c r="Y16">
+        <v>0.0298278212406136</v>
+      </c>
+      <c r="Z16">
+        <v>0.5017719525229228</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06541264094690358</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06541264094690358</v>
+      </c>
+      <c r="AD16">
+        <v>2.76</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>2.76</v>
+      </c>
+      <c r="AG16">
+        <v>-514.64</v>
+      </c>
+      <c r="AH16">
+        <v>0.007152853366505986</v>
+      </c>
+      <c r="AI16">
+        <v>0.003268747927424321</v>
+      </c>
+      <c r="AJ16">
+        <v>3.912422076934774</v>
+      </c>
+      <c r="AK16">
+        <v>-1.574015170051382</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ajman Bank PJSC (DFM:AJMANBANK)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.0272</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-3.67</v>
+      </c>
+      <c r="L17">
+        <v>-0.03491912464319696</v>
+      </c>
+      <c r="M17">
+        <v>21.7</v>
+      </c>
+      <c r="N17">
+        <v>0.01732673267326732</v>
+      </c>
+      <c r="O17">
+        <v>-5.912806539509536</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>21.7</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1074.4</v>
+      </c>
+      <c r="V17">
+        <v>0.8578728840625999</v>
+      </c>
+      <c r="W17">
+        <v>-0.004510816125860373</v>
+      </c>
+      <c r="X17">
+        <v>0.06548104289717256</v>
+      </c>
+      <c r="Y17">
+        <v>-0.06999185902303294</v>
+      </c>
+      <c r="Z17">
+        <v>3.13731343283581</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06542855949119789</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06542855949119789</v>
+      </c>
+      <c r="AD17">
+        <v>3.57</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>3.57</v>
+      </c>
+      <c r="AG17">
+        <v>-1070.83</v>
+      </c>
+      <c r="AH17">
+        <v>0.002842424580204941</v>
+      </c>
+      <c r="AI17">
+        <v>0.004316442380935107</v>
+      </c>
+      <c r="AJ17">
+        <v>-5.897615244809168</v>
+      </c>
+      <c r="AK17">
+        <v>4.329559697570046</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>National Bank of Umm Al-Qaiwain (PSC) (ADX:NBQ)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0517</v>
+      </c>
+      <c r="E18">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>140.8</v>
+      </c>
+      <c r="L18">
+        <v>0.7139959432048683</v>
+      </c>
+      <c r="M18">
+        <v>81.7</v>
+      </c>
+      <c r="N18">
+        <v>0.06820268803739878</v>
+      </c>
+      <c r="O18">
+        <v>0.5802556818181818</v>
+      </c>
+      <c r="P18">
+        <v>81.7</v>
+      </c>
+      <c r="Q18">
+        <v>0.06820268803739878</v>
+      </c>
+      <c r="R18">
+        <v>0.5802556818181818</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>1177.6</v>
+      </c>
+      <c r="V18">
+        <v>0.9830536772685532</v>
+      </c>
+      <c r="W18">
+        <v>0.09341206130166524</v>
+      </c>
+      <c r="X18">
+        <v>0.06544859829176362</v>
+      </c>
+      <c r="Y18">
+        <v>0.02796346300990162</v>
+      </c>
+      <c r="Z18">
+        <v>0.7576689002274545</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06543545201468012</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06543545201468012</v>
+      </c>
+      <c r="AD18">
+        <v>0.776</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0.776</v>
+      </c>
+      <c r="AG18">
+        <v>-1176.824</v>
+      </c>
+      <c r="AH18">
+        <v>0.0006473809436411507</v>
+      </c>
+      <c r="AI18">
+        <v>0.0004899064127234251</v>
+      </c>
+      <c r="AJ18">
+        <v>-55.83716075156509</v>
+      </c>
+      <c r="AK18">
+        <v>-2.895899364135675</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
         <v>0</v>
       </c>
     </row>
